--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -912,63 +912,66 @@
   </si>
   <si>
     <t>214
-144</t>
-  </si>
-  <si>
-    <t>62</t>
-  </si>
-  <si>
-    <t>R$ 1.411.585,28</t>
-  </si>
-  <si>
-    <t>R$ 9.286,75
-R$ 9.441,51</t>
-  </si>
-  <si>
-    <t>(2.7%)
-(1.1%)</t>
-  </si>
-  <si>
-    <t>98.3</t>
-  </si>
-  <si>
-    <t>(4.6%)</t>
-  </si>
-  <si>
-    <t>9.5%</t>
-  </si>
-  <si>
-    <t>(42.5%)</t>
-  </si>
-  <si>
-    <t>2.4%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>31.2</t>
-  </si>
-  <si>
-    <t>58.2%</t>
-  </si>
-  <si>
-    <t>16.3%</t>
-  </si>
-  <si>
-    <t>6.1</t>
-  </si>
-  <si>
-    <t>9.8</t>
-  </si>
-  <si>
-    <t>22.4</t>
-  </si>
-  <si>
-    <t>63.7%</t>
-  </si>
-  <si>
-    <t>-R$ 31.626,63</t>
+167</t>
+  </si>
+  <si>
+    <t>36</t>
+  </si>
+  <si>
+    <t>R$ 1.581.523,87</t>
+  </si>
+  <si>
+    <t>R$ 8.884,97
+R$ 9.098,55</t>
+  </si>
+  <si>
+    <t>(4.4%)
+(2.1%)</t>
+  </si>
+  <si>
+    <t>94.3</t>
+  </si>
+  <si>
+    <t>(6.7%)</t>
+  </si>
+  <si>
+    <t>10.2%</t>
+  </si>
+  <si>
+    <t>(41.3%)</t>
+  </si>
+  <si>
+    <t>2.6%</t>
+  </si>
+  <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>32.3</t>
+  </si>
+  <si>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>17.6%</t>
+  </si>
+  <si>
+    <t>6.3</t>
+  </si>
+  <si>
+    <t>10.3</t>
+  </si>
+  <si>
+    <t>16.6</t>
+  </si>
+  <si>
+    <t>22.9</t>
+  </si>
+  <si>
+    <t>62.3%</t>
+  </si>
+  <si>
+    <t>-R$ 35.271,90</t>
   </si>
   <si>
     <t>2.94</t>
@@ -1750,7 +1753,9 @@
       <c r="AB3" s="8">
         <v>4.0821763888888887</v>
       </c>
-      <c r="AC3" s="8"/>
+      <c r="AC3" s="8">
+        <v>9.5346860000000007</v>
+      </c>
       <c r="AD3" s="8">
         <v>16.408447945205481</v>
       </c>
@@ -1879,7 +1884,9 @@
       <c r="AB4" s="8">
         <v>5.0304530864197528</v>
       </c>
-      <c r="AC4" s="8"/>
+      <c r="AC4" s="8">
+        <v>13.507818</v>
+      </c>
       <c r="AD4" s="8">
         <v>18.736625925925924</v>
       </c>
@@ -2008,7 +2015,9 @@
       <c r="AB5" s="8">
         <v>14.364260824742269</v>
       </c>
-      <c r="AC5" s="8"/>
+      <c r="AC5" s="8">
+        <v>19.560261000000001</v>
+      </c>
       <c r="AD5" s="8">
         <v>24.970500000000001</v>
       </c>
@@ -2230,7 +2239,9 @@
       <c r="AB7" s="8">
         <v>1.7563829787234042</v>
       </c>
-      <c r="AC7" s="8"/>
+      <c r="AC7" s="8">
+        <v>9.8053819999999998</v>
+      </c>
       <c r="AD7" s="8">
         <v>16.815602127659574</v>
       </c>
@@ -2361,7 +2372,9 @@
       <c r="AB8" s="8">
         <v>2.8036504761904766</v>
       </c>
-      <c r="AC8" s="8"/>
+      <c r="AC8" s="8">
+        <v>8.7728560000000009</v>
+      </c>
       <c r="AD8" s="8">
         <v>15.726825714285715</v>
       </c>
@@ -2490,7 +2503,9 @@
       <c r="AB9" s="8">
         <v>4.1559210526315793</v>
       </c>
-      <c r="AC9" s="8"/>
+      <c r="AC9" s="8">
+        <v>12.469735999999999</v>
+      </c>
       <c r="AD9" s="8">
         <v>18.55263157894737</v>
       </c>
@@ -2617,7 +2632,9 @@
       <c r="AB10" s="8">
         <v>2.7005882352941177</v>
       </c>
-      <c r="AC10" s="8"/>
+      <c r="AC10" s="8">
+        <v>9.6615719999999996</v>
+      </c>
       <c r="AD10" s="8">
         <v>16.513529411764708</v>
       </c>
@@ -2746,7 +2763,9 @@
       <c r="AB11" s="8">
         <v>5.9500000000000002</v>
       </c>
-      <c r="AC11" s="8"/>
+      <c r="AC11" s="8">
+        <v>11.375</v>
+      </c>
       <c r="AD11" s="8">
         <v>17.205219191919191</v>
       </c>
@@ -3004,7 +3023,9 @@
       <c r="AB13" s="8">
         <v>6.7145094117647055</v>
       </c>
-      <c r="AC13" s="8"/>
+      <c r="AC13" s="8">
+        <v>12.132548</v>
+      </c>
       <c r="AD13" s="8">
         <v>19.079608235294117</v>
       </c>
@@ -3133,7 +3154,9 @@
       <c r="AB14" s="8">
         <v>3.467543609022556</v>
       </c>
-      <c r="AC14" s="8"/>
+      <c r="AC14" s="8">
+        <v>10.260901</v>
+      </c>
       <c r="AD14" s="8">
         <v>17.220050375939852</v>
       </c>
@@ -3262,7 +3285,9 @@
       <c r="AB15" s="8">
         <v>3.5438991071428569</v>
       </c>
-      <c r="AC15" s="8"/>
+      <c r="AC15" s="8">
+        <v>12.038487999999999</v>
+      </c>
       <c r="AD15" s="8">
         <v>18.864327192982458</v>
       </c>
@@ -3391,7 +3416,9 @@
       <c r="AB16" s="8">
         <v>61.109090909090916</v>
       </c>
-      <c r="AC16" s="8"/>
+      <c r="AC16" s="8">
+        <v>71.628534000000002</v>
+      </c>
       <c r="AD16" s="8">
         <v>72.543652380952381</v>
       </c>
@@ -3520,7 +3547,9 @@
       <c r="AB17" s="8">
         <v>3.1699535211267604</v>
       </c>
-      <c r="AC17" s="8"/>
+      <c r="AC17" s="8">
+        <v>6.3905149999999997</v>
+      </c>
       <c r="AD17" s="8">
         <v>14.010360810810809</v>
       </c>
@@ -3649,7 +3678,9 @@
       <c r="AB18" s="8">
         <v>4.9463495238095243</v>
       </c>
-      <c r="AC18" s="8"/>
+      <c r="AC18" s="8">
+        <v>9.7136379999999996</v>
+      </c>
       <c r="AD18" s="8">
         <v>16.485046728971962</v>
       </c>
@@ -3778,7 +3809,9 @@
       <c r="AB19" s="8">
         <v>15.983567605633803</v>
       </c>
-      <c r="AC19" s="8"/>
+      <c r="AC19" s="8">
+        <v>23.501622999999999</v>
+      </c>
       <c r="AD19" s="8">
         <v>30.2004625</v>
       </c>
@@ -3907,7 +3940,9 @@
       <c r="AB20" s="8">
         <v>6.8659999999999997</v>
       </c>
-      <c r="AC20" s="8"/>
+      <c r="AC20" s="8">
+        <v>26.768238</v>
+      </c>
       <c r="AD20" s="8">
         <v>32.789276744186047</v>
       </c>
@@ -4036,7 +4071,9 @@
       <c r="AB21" s="8">
         <v>4.8867346938775507</v>
       </c>
-      <c r="AC21" s="8"/>
+      <c r="AC21" s="8">
+        <v>7.3588420000000001</v>
+      </c>
       <c r="AD21" s="8">
         <v>13.313606122448981</v>
       </c>
@@ -4165,7 +4202,9 @@
       <c r="AB22" s="8">
         <v>4.1024752475247528</v>
       </c>
-      <c r="AC22" s="8"/>
+      <c r="AC22" s="8">
+        <v>11.994467999999999</v>
+      </c>
       <c r="AD22" s="8">
         <v>18.871287128712872</v>
       </c>
@@ -4294,7 +4333,9 @@
       <c r="AB23" s="8">
         <v>4.5869961538461537</v>
       </c>
-      <c r="AC23" s="8"/>
+      <c r="AC23" s="8">
+        <v>12.669976</v>
+      </c>
       <c r="AD23" s="8">
         <v>19.31031746031746</v>
       </c>
@@ -4518,7 +4559,9 @@
       <c r="AB25" s="8">
         <v>9.737689772727272</v>
       </c>
-      <c r="AC25" s="8"/>
+      <c r="AC25" s="8">
+        <v>18.174868</v>
+      </c>
       <c r="AD25" s="8">
         <v>24.886142696629214</v>
       </c>
@@ -4647,7 +4690,9 @@
       <c r="AB26" s="8">
         <v>10.674927826086957</v>
       </c>
-      <c r="AC26" s="8"/>
+      <c r="AC26" s="8">
+        <v>16.047288000000002</v>
+      </c>
       <c r="AD26" s="8">
         <v>21.877731967213112</v>
       </c>
@@ -4698,7 +4743,7 @@
         <v>19545</v>
       </c>
       <c r="B27" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C27" s="4">
         <v>44</v>
@@ -4734,25 +4779,59 @@
       <c t="s" r="N27" s="4">
         <v>52</v>
       </c>
-      <c r="O27" s="5"/>
-      <c r="P27" s="5"/>
-      <c r="Q27" s="6"/>
-      <c r="R27" s="7"/>
-      <c r="S27" s="6"/>
-      <c r="T27" s="6"/>
-      <c r="U27" s="6"/>
-      <c r="V27" s="6"/>
-      <c r="W27" s="6"/>
-      <c r="X27" s="8"/>
-      <c r="Y27" s="6"/>
-      <c r="Z27" s="6"/>
-      <c r="AA27" s="8"/>
-      <c r="AB27" s="8"/>
+      <c r="O27" s="5">
+        <v>7627.6899999999996</v>
+      </c>
+      <c r="P27" s="5">
+        <v>7627.6899999999996</v>
+      </c>
+      <c r="Q27" s="6">
+        <v>-0.42624012540788403</v>
+      </c>
+      <c r="R27" s="7">
+        <v>70</v>
+      </c>
+      <c r="S27" s="6">
+        <v>-0.52054794520547953</v>
+      </c>
+      <c r="T27" s="6">
+        <v>0.34091940023781775</v>
+      </c>
+      <c r="U27" s="6">
+        <v>-0.064812872573478994</v>
+      </c>
+      <c r="V27" s="6">
+        <v>0.010918312097109348</v>
+      </c>
+      <c r="W27" s="6">
+        <v>-5.4865889935222856E-05</v>
+      </c>
+      <c r="X27" s="8">
+        <v>26.538889743589742</v>
+      </c>
+      <c r="Y27" s="6">
+        <v>0.48780487804878048</v>
+      </c>
+      <c r="Z27" s="6">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AA27" s="8">
+        <v>5.5073814285714286</v>
+      </c>
+      <c r="AB27" s="8">
+        <v>7.037179487179487</v>
+      </c>
       <c r="AC27" s="8"/>
-      <c r="AD27" s="8"/>
-      <c r="AE27" s="6"/>
+      <c r="AD27" s="8">
+        <v>20.712392307692308</v>
+      </c>
+      <c r="AE27" s="6">
+        <v>0.64102564102564108</v>
+      </c>
       <c r="AF27" s="9"/>
-      <c r="AG27" s="5"/>
+      <c r="AG27" s="5">
+        <v>-543.32000000000005</v>
+      </c>
       <c r="AH27" s="10">
         <v>2</v>
       </c>
@@ -4871,7 +4950,9 @@
       <c r="AB28" s="8">
         <v>6.7096491228070176</v>
       </c>
-      <c r="AC28" s="8"/>
+      <c r="AC28" s="8">
+        <v>9.235087</v>
+      </c>
       <c r="AD28" s="8">
         <v>16.173391228070173</v>
       </c>
@@ -5000,7 +5081,9 @@
       <c r="AB29" s="8">
         <v>13.548958750000001</v>
       </c>
-      <c r="AC29" s="8"/>
+      <c r="AC29" s="8">
+        <v>22.141234000000001</v>
+      </c>
       <c r="AD29" s="8">
         <v>29.62012195121951</v>
       </c>
@@ -5125,7 +5208,9 @@
       <c r="AB30" s="8">
         <v>6.4562499999999998</v>
       </c>
-      <c r="AC30" s="8"/>
+      <c r="AC30" s="8">
+        <v>8.6993050000000007</v>
+      </c>
       <c r="AD30" s="8">
         <v>15.666666666666666</v>
       </c>
@@ -5256,7 +5341,9 @@
       <c r="AB31" s="8">
         <v>5.4949565789473684</v>
       </c>
-      <c r="AC31" s="8"/>
+      <c r="AC31" s="8">
+        <v>12.781031</v>
+      </c>
       <c r="AD31" s="8">
         <v>20.549358974358974</v>
       </c>
@@ -5385,7 +5472,9 @@
       <c r="AB32" s="8">
         <v>6.0780262569832395</v>
       </c>
-      <c r="AC32" s="8"/>
+      <c r="AC32" s="8">
+        <v>12.267225</v>
+      </c>
       <c r="AD32" s="8">
         <v>18.225232960893855</v>
       </c>
@@ -5512,7 +5601,9 @@
       <c r="AB33" s="8">
         <v>4.9253092592592589</v>
       </c>
-      <c r="AC33" s="8"/>
+      <c r="AC33" s="8">
+        <v>7.4878080000000002</v>
+      </c>
       <c r="AD33" s="8">
         <v>14.454629629629629</v>
       </c>
@@ -5738,7 +5829,9 @@
       <c r="AB35" s="8">
         <v>4.0948490909090909</v>
       </c>
-      <c r="AC35" s="8"/>
+      <c r="AC35" s="8">
+        <v>8.7090899999999998</v>
+      </c>
       <c r="AD35" s="8">
         <v>15.662121818181818</v>
       </c>
@@ -5964,7 +6057,9 @@
       <c r="AB37" s="8">
         <v>10.245238571428571</v>
       </c>
-      <c r="AC37" s="8"/>
+      <c r="AC37" s="8">
+        <v>15.16146</v>
+      </c>
       <c r="AD37" s="8">
         <v>21.618055555555557</v>
       </c>
@@ -6093,7 +6188,9 @@
       <c r="AB38" s="8">
         <v>12.181783720930232</v>
       </c>
-      <c r="AC38" s="8"/>
+      <c r="AC38" s="8">
+        <v>15.131781999999999</v>
+      </c>
       <c r="AD38" s="8">
         <v>21.706818181818182</v>
       </c>
@@ -6144,7 +6241,7 @@
         <v>19565</v>
       </c>
       <c r="B39" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C39" s="4">
         <v>44</v>
@@ -6180,25 +6277,59 @@
       <c t="s" r="N39" s="4">
         <v>52</v>
       </c>
-      <c r="O39" s="5"/>
-      <c r="P39" s="5"/>
-      <c r="Q39" s="6"/>
-      <c r="R39" s="7"/>
-      <c r="S39" s="6"/>
-      <c r="T39" s="6"/>
-      <c r="U39" s="6"/>
-      <c r="V39" s="6"/>
-      <c r="W39" s="6"/>
-      <c r="X39" s="8"/>
-      <c r="Y39" s="6"/>
-      <c r="Z39" s="6"/>
-      <c r="AA39" s="8"/>
-      <c r="AB39" s="8"/>
+      <c r="O39" s="5">
+        <v>8480.75</v>
+      </c>
+      <c r="P39" s="5">
+        <v>8480.75</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>-0.1681632845228298</v>
+      </c>
+      <c r="R39" s="7">
+        <v>91</v>
+      </c>
+      <c r="S39" s="6">
+        <v>-0.20175438596491224</v>
+      </c>
+      <c r="T39" s="6">
+        <v>0.29145044954750465</v>
+      </c>
+      <c r="U39" s="6">
+        <v>-0.031847607817704807</v>
+      </c>
+      <c r="V39" s="6">
+        <v>0.068168499248297612</v>
+      </c>
+      <c r="W39" s="6">
+        <v>0.039263036877634647</v>
+      </c>
+      <c r="X39" s="8">
+        <v>22.77410714285714</v>
+      </c>
+      <c r="Y39" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="6">
+        <v>0.017857142857142856</v>
+      </c>
+      <c r="AA39" s="8">
+        <v>3.2839011363636361</v>
+      </c>
+      <c r="AB39" s="8">
+        <v>5.9204081632653063</v>
+      </c>
       <c r="AC39" s="8"/>
-      <c r="AD39" s="8"/>
-      <c r="AE39" s="6"/>
+      <c r="AD39" s="8">
+        <v>15.408630357142856</v>
+      </c>
+      <c r="AE39" s="6">
+        <v>0.8928571428571429</v>
+      </c>
       <c r="AF39" s="9"/>
-      <c r="AG39" s="5"/>
+      <c r="AG39" s="5">
+        <v>0</v>
+      </c>
       <c r="AH39" s="10">
         <v>4</v>
       </c>
@@ -6317,7 +6448,9 @@
       <c r="AB40" s="8">
         <v>14.926557476635514</v>
       </c>
-      <c r="AC40" s="8"/>
+      <c r="AC40" s="8">
+        <v>20.076025999999999</v>
+      </c>
       <c r="AD40" s="8">
         <v>26.68079861751152</v>
       </c>
@@ -6446,7 +6579,9 @@
       <c r="AB41" s="8">
         <v>25.689305833333332</v>
       </c>
-      <c r="AC41" s="8"/>
+      <c r="AC41" s="8">
+        <v>29.914173999999999</v>
+      </c>
       <c r="AD41" s="8">
         <v>34.703091129032252</v>
       </c>
@@ -6592,7 +6727,7 @@
         <v>19580</v>
       </c>
       <c r="B43" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C43" s="4">
         <v>44</v>
@@ -6628,25 +6763,59 @@
       <c t="s" r="N43" s="4">
         <v>52</v>
       </c>
-      <c r="O43" s="5"/>
-      <c r="P43" s="5"/>
-      <c r="Q43" s="6"/>
-      <c r="R43" s="7"/>
-      <c r="S43" s="6"/>
-      <c r="T43" s="6"/>
-      <c r="U43" s="6"/>
-      <c r="V43" s="6"/>
-      <c r="W43" s="6"/>
-      <c r="X43" s="8"/>
-      <c r="Y43" s="6"/>
-      <c r="Z43" s="6"/>
-      <c r="AA43" s="8"/>
-      <c r="AB43" s="8"/>
+      <c r="O43" s="5">
+        <v>10237.200000000001</v>
+      </c>
+      <c r="P43" s="5">
+        <v>10237.200000000001</v>
+      </c>
+      <c r="Q43" s="6">
+        <v>0.11719211247439532</v>
+      </c>
+      <c r="R43" s="7">
+        <v>90</v>
+      </c>
+      <c r="S43" s="6">
+        <v>-0.11764705882352944</v>
+      </c>
+      <c r="T43" s="6">
+        <v>-7.3936232563591599E-05</v>
+      </c>
+      <c r="U43" s="6">
+        <v>-0.3988704821630914</v>
+      </c>
+      <c r="V43" s="6">
+        <v>0.019967764623139136</v>
+      </c>
+      <c r="W43" s="6">
+        <v>0.0040200445434298441</v>
+      </c>
+      <c r="X43" s="8">
+        <v>40.199757971014492</v>
+      </c>
+      <c r="Y43" s="6">
+        <v>0.36231884057971014</v>
+      </c>
+      <c r="Z43" s="6">
+        <v>0.52173913043478259</v>
+      </c>
+      <c r="AA43" s="8">
+        <v>11.889560439560441</v>
+      </c>
+      <c r="AB43" s="8">
+        <v>9.3499999999999996</v>
+      </c>
       <c r="AC43" s="8"/>
-      <c r="AD43" s="8"/>
-      <c r="AE43" s="6"/>
+      <c r="AD43" s="8">
+        <v>28.964734782608698</v>
+      </c>
+      <c r="AE43" s="6">
+        <v>0.14492753623188406</v>
+      </c>
       <c r="AF43" s="9"/>
-      <c r="AG43" s="5"/>
+      <c r="AG43" s="5">
+        <v>0</v>
+      </c>
       <c r="AH43" s="10">
         <v>1</v>
       </c>
@@ -6765,7 +6934,9 @@
       <c r="AB44" s="8">
         <v>4.3985294117647058</v>
       </c>
-      <c r="AC44" s="8"/>
+      <c r="AC44" s="8">
+        <v>8.9587020000000006</v>
+      </c>
       <c r="AD44" s="8">
         <v>12.415367532467533</v>
       </c>
@@ -6894,7 +7065,9 @@
       <c r="AB45" s="8">
         <v>3.7606421686746989</v>
       </c>
-      <c r="AC45" s="8"/>
+      <c r="AC45" s="8">
+        <v>7.5035249999999998</v>
+      </c>
       <c r="AD45" s="8">
         <v>13.753413253012049</v>
       </c>
@@ -6945,7 +7118,7 @@
         <v>19596</v>
       </c>
       <c r="B46" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C46" s="4">
         <v>44</v>
@@ -6979,25 +7152,59 @@
       <c t="s" r="N46" s="4">
         <v>52</v>
       </c>
-      <c r="O46" s="5"/>
-      <c r="P46" s="5"/>
-      <c r="Q46" s="6"/>
-      <c r="R46" s="7"/>
-      <c r="S46" s="6"/>
-      <c r="T46" s="6"/>
-      <c r="U46" s="6"/>
-      <c r="V46" s="6"/>
-      <c r="W46" s="6"/>
-      <c r="X46" s="8"/>
-      <c r="Y46" s="6"/>
-      <c r="Z46" s="6"/>
-      <c r="AA46" s="8"/>
-      <c r="AB46" s="8"/>
+      <c r="O46" s="5">
+        <v>9646.3999999999996</v>
+      </c>
+      <c r="P46" s="5">
+        <v>9646.3999999999996</v>
+      </c>
+      <c r="Q46" s="6">
+        <v>-0.073192290693876116</v>
+      </c>
+      <c r="R46" s="7">
+        <v>110</v>
+      </c>
+      <c r="S46" s="6">
+        <v>-0.017857142857142905</v>
+      </c>
+      <c r="T46" s="6">
+        <v>0.054312842096533427</v>
+      </c>
+      <c r="U46" s="6">
+        <v>-0.27915767540222258</v>
+      </c>
+      <c r="V46" s="6">
+        <v>0.024188090894012276</v>
+      </c>
+      <c r="W46" s="6">
+        <v>-0.020530145961187594</v>
+      </c>
+      <c r="X46" s="8">
+        <v>26.904285714285713</v>
+      </c>
+      <c r="Y46" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="6">
+        <v>0.042857142857142858</v>
+      </c>
+      <c r="AA46" s="8">
+        <v>3.1669811320754717</v>
+      </c>
+      <c r="AB46" s="8">
+        <v>8.3869042857142855</v>
+      </c>
       <c r="AC46" s="8"/>
-      <c r="AD46" s="8"/>
-      <c r="AE46" s="6"/>
+      <c r="AD46" s="8">
+        <v>18.806189999999997</v>
+      </c>
+      <c r="AE46" s="6">
+        <v>0.68571428571428572</v>
+      </c>
       <c r="AF46" s="9"/>
-      <c r="AG46" s="5"/>
+      <c r="AG46" s="5">
+        <v>241.5</v>
+      </c>
       <c r="AH46" s="10">
         <v>3</v>
       </c>
@@ -7116,7 +7323,9 @@
       <c r="AB47" s="8">
         <v>12.128114141414141</v>
       </c>
-      <c r="AC47" s="8"/>
+      <c r="AC47" s="8">
+        <v>18.683506000000001</v>
+      </c>
       <c r="AD47" s="8">
         <v>25.359076237623764</v>
       </c>
@@ -7243,7 +7452,9 @@
       <c r="AB48" s="8">
         <v>18.331597916666666</v>
       </c>
-      <c r="AC48" s="8"/>
+      <c r="AC48" s="8">
+        <v>32.663327000000002</v>
+      </c>
       <c r="AD48" s="8">
         <v>38.981291836734691</v>
       </c>
@@ -7370,7 +7581,9 @@
       <c r="AB49" s="8">
         <v>7.5967683673469386</v>
       </c>
-      <c r="AC49" s="8"/>
+      <c r="AC49" s="8">
+        <v>11.912255999999999</v>
+      </c>
       <c r="AD49" s="8">
         <v>19.865986734693877</v>
       </c>
@@ -7421,7 +7634,7 @@
         <v>19601</v>
       </c>
       <c r="B50" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C50" s="4">
         <v>44</v>
@@ -7457,25 +7670,59 @@
       <c t="s" r="N50" s="4">
         <v>52</v>
       </c>
-      <c r="O50" s="5"/>
-      <c r="P50" s="5"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="7"/>
-      <c r="S50" s="6"/>
-      <c r="T50" s="6"/>
-      <c r="U50" s="6"/>
-      <c r="V50" s="6"/>
-      <c r="W50" s="6"/>
-      <c r="X50" s="8"/>
-      <c r="Y50" s="6"/>
-      <c r="Z50" s="6"/>
-      <c r="AA50" s="8"/>
-      <c r="AB50" s="8"/>
+      <c r="O50" s="5">
+        <v>6839.8699999999999</v>
+      </c>
+      <c r="P50" s="5">
+        <v>6839.8699999999999</v>
+      </c>
+      <c r="Q50" s="6">
+        <v>-0.26163540072153846</v>
+      </c>
+      <c r="R50" s="7">
+        <v>81</v>
+      </c>
+      <c r="S50" s="6">
+        <v>-0.23584905660377353</v>
+      </c>
+      <c r="T50" s="6">
+        <v>0.2359966051986368</v>
+      </c>
+      <c r="U50" s="6">
+        <v>-0.065500353076885967</v>
+      </c>
+      <c r="V50" s="6">
+        <v>0.10390263265237498</v>
+      </c>
+      <c r="W50" s="6">
+        <v>0.065412135025958093</v>
+      </c>
+      <c r="X50" s="8">
+        <v>21.850327450980394</v>
+      </c>
+      <c r="Y50" s="6">
+        <v>0.96078431372549022</v>
+      </c>
+      <c r="Z50" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA50" s="8">
+        <v>2.6732063291139241</v>
+      </c>
+      <c r="AB50" s="8">
+        <v>3.1123340000000002</v>
+      </c>
       <c r="AC50" s="8"/>
-      <c r="AD50" s="8"/>
-      <c r="AE50" s="6"/>
+      <c r="AD50" s="8">
+        <v>13.683333333333334</v>
+      </c>
+      <c r="AE50" s="6">
+        <v>0.94117647058823528</v>
+      </c>
       <c r="AF50" s="9"/>
-      <c r="AG50" s="5"/>
+      <c r="AG50" s="5">
+        <v>-62.890000000000001</v>
+      </c>
       <c r="AH50" s="10">
         <v>4</v>
       </c>
@@ -7689,7 +7936,9 @@
       <c r="AB52" s="8">
         <v>9.076766666666666</v>
       </c>
-      <c r="AC52" s="8"/>
+      <c r="AC52" s="8">
+        <v>14.434862000000001</v>
+      </c>
       <c r="AD52" s="8">
         <v>21.62857142857143</v>
       </c>
@@ -7816,7 +8065,9 @@
       <c r="AB53" s="8">
         <v>3.9555562500000003</v>
       </c>
-      <c r="AC53" s="8"/>
+      <c r="AC53" s="8">
+        <v>8.1878460000000004</v>
+      </c>
       <c r="AD53" s="8">
         <v>15.087847916666666</v>
       </c>
@@ -7945,7 +8196,9 @@
       <c r="AB54" s="8">
         <v>6.9385051724137927</v>
       </c>
-      <c r="AC54" s="8"/>
+      <c r="AC54" s="8">
+        <v>12.886623</v>
+      </c>
       <c r="AD54" s="8">
         <v>19.664123728813557</v>
       </c>
@@ -7996,7 +8249,7 @@
         <v>19615</v>
       </c>
       <c r="B55" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C55" s="4">
         <v>44</v>
@@ -8032,25 +8285,59 @@
       <c t="s" r="N55" s="4">
         <v>52</v>
       </c>
-      <c r="O55" s="5"/>
-      <c r="P55" s="5"/>
-      <c r="Q55" s="6"/>
-      <c r="R55" s="7"/>
-      <c r="S55" s="6"/>
-      <c r="T55" s="6"/>
-      <c r="U55" s="6"/>
-      <c r="V55" s="6"/>
-      <c r="W55" s="6"/>
-      <c r="X55" s="8"/>
-      <c r="Y55" s="6"/>
-      <c r="Z55" s="6"/>
-      <c r="AA55" s="8"/>
-      <c r="AB55" s="8"/>
+      <c r="O55" s="5">
+        <v>5640.3999999999996</v>
+      </c>
+      <c r="P55" s="5">
+        <v>5640.3999999999996</v>
+      </c>
+      <c r="Q55" s="6">
+        <v>-0.39938750388666699</v>
+      </c>
+      <c r="R55" s="7">
+        <v>68</v>
+      </c>
+      <c r="S55" s="6">
+        <v>-0.30612244897959184</v>
+      </c>
+      <c r="T55" s="6">
+        <v>0</v>
+      </c>
+      <c r="U55" s="6">
+        <v>-0.34340117722147367</v>
+      </c>
+      <c r="V55" s="6">
+        <v>0.052704506772569326</v>
+      </c>
+      <c r="W55" s="6">
+        <v>0.024444099709240483</v>
+      </c>
+      <c r="X55" s="8">
+        <v>59.094230769230769</v>
+      </c>
+      <c r="Y55" s="6">
+        <v>0.038461538461538464</v>
+      </c>
+      <c r="Z55" s="6">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="AA55" s="8">
+        <v>3.9068070422535213</v>
+      </c>
+      <c r="AB55" s="8">
+        <v>38.469230769230769</v>
+      </c>
       <c r="AC55" s="8"/>
-      <c r="AD55" s="8"/>
-      <c r="AE55" s="6"/>
+      <c r="AD55" s="8">
+        <v>49.247115384615384</v>
+      </c>
+      <c r="AE55" s="6">
+        <v>0</v>
+      </c>
       <c r="AF55" s="9"/>
-      <c r="AG55" s="5"/>
+      <c r="AG55" s="5">
+        <v>0</v>
+      </c>
       <c r="AH55" s="10">
         <v>2</v>
       </c>
@@ -8167,7 +8454,9 @@
       <c r="AB56" s="8">
         <v>10.587318840579711</v>
       </c>
-      <c r="AC56" s="8"/>
+      <c r="AC56" s="8">
+        <v>17.18544</v>
+      </c>
       <c r="AD56" s="8">
         <v>25.213497887323943</v>
       </c>
@@ -8296,7 +8585,9 @@
       <c r="AB57" s="8">
         <v>7.1038461538461535</v>
       </c>
-      <c r="AC57" s="8"/>
+      <c r="AC57" s="8">
+        <v>14.372363999999999</v>
+      </c>
       <c r="AD57" s="8">
         <v>21.375961538461539</v>
       </c>
@@ -8520,7 +8811,9 @@
       <c r="AB59" s="8">
         <v>4.997436538461538</v>
       </c>
-      <c r="AC59" s="8"/>
+      <c r="AC59" s="8">
+        <v>9.3502650000000003</v>
+      </c>
       <c r="AD59" s="8">
         <v>16.14119433962264</v>
       </c>
@@ -8649,7 +8942,9 @@
       <c r="AB60" s="8">
         <v>5.1838393939393939</v>
       </c>
-      <c r="AC60" s="8"/>
+      <c r="AC60" s="8">
+        <v>8.5107979999999994</v>
+      </c>
       <c r="AD60" s="8">
         <v>16.230882352941176</v>
       </c>
@@ -8776,7 +9071,9 @@
       <c r="AB61" s="8">
         <v>8.5545454545454547</v>
       </c>
-      <c r="AC61" s="8"/>
+      <c r="AC61" s="8">
+        <v>11.103354</v>
+      </c>
       <c r="AD61" s="8">
         <v>16.565384615384616</v>
       </c>
@@ -8825,7 +9122,7 @@
         <v>19625</v>
       </c>
       <c r="B62" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C62" s="4">
         <v>44</v>
@@ -8861,25 +9158,59 @@
       <c t="s" r="N62" s="4">
         <v>52</v>
       </c>
-      <c r="O62" s="5"/>
-      <c r="P62" s="5"/>
-      <c r="Q62" s="6"/>
-      <c r="R62" s="7"/>
-      <c r="S62" s="6"/>
-      <c r="T62" s="6"/>
-      <c r="U62" s="6"/>
-      <c r="V62" s="6"/>
-      <c r="W62" s="6"/>
-      <c r="X62" s="8"/>
-      <c r="Y62" s="6"/>
-      <c r="Z62" s="6"/>
-      <c r="AA62" s="8"/>
-      <c r="AB62" s="8"/>
+      <c r="O62" s="5">
+        <v>8435.2800000000007</v>
+      </c>
+      <c r="P62" s="5">
+        <v>8435.2800000000007</v>
+      </c>
+      <c r="Q62" s="6">
+        <v>-0.14548291022549986</v>
+      </c>
+      <c r="R62" s="7">
+        <v>81</v>
+      </c>
+      <c r="S62" s="6">
+        <v>-0.22115384615384615</v>
+      </c>
+      <c r="T62" s="6">
+        <v>0.0002406203469238721</v>
+      </c>
+      <c r="U62" s="6">
+        <v>-0.29641461812767328</v>
+      </c>
+      <c r="V62" s="6">
+        <v>0.044910127464648474</v>
+      </c>
+      <c r="W62" s="6">
+        <v>0.029075442664618124</v>
+      </c>
+      <c r="X62" s="8">
+        <v>23.866986538461539</v>
+      </c>
+      <c r="Y62" s="6">
+        <v>0.80769230769230771</v>
+      </c>
+      <c r="Z62" s="6">
+        <v>0.057692307692307696</v>
+      </c>
+      <c r="AA62" s="8">
+        <v>3.0720879518072293</v>
+      </c>
+      <c r="AB62" s="8">
+        <v>4.8700000000000001</v>
+      </c>
       <c r="AC62" s="8"/>
-      <c r="AD62" s="8"/>
-      <c r="AE62" s="6"/>
+      <c r="AD62" s="8">
+        <v>14.80673076923077</v>
+      </c>
+      <c r="AE62" s="6">
+        <v>0.84615384615384615</v>
+      </c>
       <c r="AF62" s="9"/>
-      <c r="AG62" s="5"/>
+      <c r="AG62" s="5">
+        <v>-104.59999999999999</v>
+      </c>
       <c r="AH62" s="10">
         <v>4</v>
       </c>
@@ -8998,7 +9329,9 @@
       <c r="AB63" s="8">
         <v>10.782366666666666</v>
       </c>
-      <c r="AC63" s="8"/>
+      <c r="AC63" s="8">
+        <v>15.813154000000001</v>
+      </c>
       <c r="AD63" s="8">
         <v>21.210879166666665</v>
       </c>
@@ -9125,7 +9458,9 @@
       <c r="AB64" s="8">
         <v>12.472805263157895</v>
       </c>
-      <c r="AC64" s="8"/>
+      <c r="AC64" s="8">
+        <v>16.670029</v>
+      </c>
       <c r="AD64" s="8">
         <v>20.065279166666667</v>
       </c>
@@ -9347,7 +9682,9 @@
       <c r="AB66" s="8">
         <v>5.4706357142857138</v>
       </c>
-      <c r="AC66" s="8"/>
+      <c r="AC66" s="8">
+        <v>9.3789669999999994</v>
+      </c>
       <c r="AD66" s="8">
         <v>16.253173809523808</v>
       </c>
@@ -9474,7 +9811,9 @@
       <c r="AB67" s="8">
         <v>15.480719607843138</v>
       </c>
-      <c r="AC67" s="8"/>
+      <c r="AC67" s="8">
+        <v>19.023218</v>
+      </c>
       <c r="AD67" s="8">
         <v>22.961388333333332</v>
       </c>
@@ -9603,7 +9942,9 @@
       <c r="AB68" s="8">
         <v>2.7605263157894737</v>
       </c>
-      <c r="AC68" s="8"/>
+      <c r="AC68" s="8">
+        <v>8.4807009999999998</v>
+      </c>
       <c r="AD68" s="8">
         <v>15.436402631578948</v>
       </c>
@@ -9726,7 +10067,9 @@
       <c r="AB69" s="8">
         <v>5.7666671052631582</v>
       </c>
-      <c r="AC69" s="8"/>
+      <c r="AC69" s="8">
+        <v>9.5143450000000005</v>
+      </c>
       <c r="AD69" s="8">
         <v>17.261965384615383</v>
       </c>
@@ -9855,7 +10198,9 @@
       <c r="AB70" s="8">
         <v>5.1515145454545452</v>
       </c>
-      <c r="AC70" s="8"/>
+      <c r="AC70" s="8">
+        <v>10.031574000000001</v>
+      </c>
       <c r="AD70" s="8">
         <v>16.833928571428572</v>
       </c>
@@ -9906,7 +10251,7 @@
         <v>19649</v>
       </c>
       <c r="B71" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C71" s="4">
         <v>44</v>
@@ -9940,25 +10285,59 @@
       <c t="s" r="N71" s="4">
         <v>52</v>
       </c>
-      <c r="O71" s="5"/>
-      <c r="P71" s="5"/>
-      <c r="Q71" s="6"/>
-      <c r="R71" s="7"/>
-      <c r="S71" s="6"/>
-      <c r="T71" s="6"/>
-      <c r="U71" s="6"/>
-      <c r="V71" s="6"/>
-      <c r="W71" s="6"/>
-      <c r="X71" s="8"/>
-      <c r="Y71" s="6"/>
-      <c r="Z71" s="6"/>
-      <c r="AA71" s="8"/>
-      <c r="AB71" s="8"/>
+      <c r="O71" s="5">
+        <v>9824.2700000000004</v>
+      </c>
+      <c r="P71" s="5">
+        <v>9824.2700000000004</v>
+      </c>
+      <c r="Q71" s="6">
+        <v>0.11954048137550188</v>
+      </c>
+      <c r="R71" s="7">
+        <v>104</v>
+      </c>
+      <c r="S71" s="6">
+        <v>-0.00952380952380949</v>
+      </c>
+      <c r="T71" s="6">
+        <v>0.28262110060085888</v>
+      </c>
+      <c r="U71" s="6">
+        <v>-0.031166081551097437</v>
+      </c>
+      <c r="V71" s="6">
+        <v>0.051103338975822123</v>
+      </c>
+      <c r="W71" s="6">
+        <v>0.021275168536695348</v>
+      </c>
+      <c r="X71" s="8">
+        <v>26.284545454545455</v>
+      </c>
+      <c r="Y71" s="6">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="Z71" s="6">
+        <v>0.018181818181818181</v>
+      </c>
+      <c r="AA71" s="8">
+        <v>4.5663303030303029</v>
+      </c>
+      <c r="AB71" s="8">
+        <v>5.1432092592592591</v>
+      </c>
       <c r="AC71" s="8"/>
-      <c r="AD71" s="8"/>
-      <c r="AE71" s="6"/>
+      <c r="AD71" s="8">
+        <v>17.166059999999998</v>
+      </c>
+      <c r="AE71" s="6">
+        <v>0.70909090909090911</v>
+      </c>
       <c r="AF71" s="9"/>
-      <c r="AG71" s="5"/>
+      <c r="AG71" s="5">
+        <v>356</v>
+      </c>
       <c r="AH71" s="10">
         <v>4</v>
       </c>
@@ -10075,7 +10454,9 @@
       <c r="AB72" s="8">
         <v>5.8191237179487185</v>
       </c>
-      <c r="AC72" s="8"/>
+      <c r="AC72" s="8">
+        <v>11.640034999999999</v>
+      </c>
       <c r="AD72" s="8">
         <v>18.540064102564102</v>
       </c>
@@ -10202,7 +10583,9 @@
       <c r="AB73" s="8">
         <v>7.1290111111111116</v>
       </c>
-      <c r="AC73" s="8"/>
+      <c r="AC73" s="8">
+        <v>9.6592199999999995</v>
+      </c>
       <c r="AD73" s="8">
         <v>16.084945161290324</v>
       </c>
@@ -10344,7 +10727,7 @@
         <v>19657</v>
       </c>
       <c r="B75" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C75" s="4">
         <v>44</v>
@@ -10380,25 +10763,59 @@
       <c t="s" r="N75" s="4">
         <v>52</v>
       </c>
-      <c r="O75" s="5"/>
-      <c r="P75" s="5"/>
-      <c r="Q75" s="6"/>
-      <c r="R75" s="7"/>
-      <c r="S75" s="6"/>
-      <c r="T75" s="6"/>
-      <c r="U75" s="6"/>
-      <c r="V75" s="6"/>
-      <c r="W75" s="6"/>
-      <c r="X75" s="8"/>
-      <c r="Y75" s="6"/>
-      <c r="Z75" s="6"/>
-      <c r="AA75" s="8"/>
-      <c r="AB75" s="8"/>
+      <c r="O75" s="5">
+        <v>5306.04</v>
+      </c>
+      <c r="P75" s="5">
+        <v>5306.04</v>
+      </c>
+      <c r="Q75" s="6">
+        <v>-0.13191347339971271</v>
+      </c>
+      <c r="R75" s="7">
+        <v>58</v>
+      </c>
+      <c r="S75" s="6">
+        <v>-0.15942028985507251</v>
+      </c>
+      <c r="T75" s="6">
+        <v>0</v>
+      </c>
+      <c r="U75" s="6">
+        <v>-0.32780378587421127</v>
+      </c>
+      <c r="V75" s="6">
+        <v>0.056937094330234979</v>
+      </c>
+      <c r="W75" s="6">
+        <v>0.03287960512924893</v>
+      </c>
+      <c r="X75" s="8">
+        <v>22.656668</v>
+      </c>
+      <c r="Y75" s="6">
+        <v>0.83999999999999997</v>
+      </c>
+      <c r="Z75" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA75" s="8">
+        <v>4.6099421052631584</v>
+      </c>
+      <c r="AB75" s="8">
+        <v>4.6576374999999999</v>
+      </c>
       <c r="AC75" s="8"/>
-      <c r="AD75" s="8"/>
-      <c r="AE75" s="6"/>
+      <c r="AD75" s="8">
+        <v>15.743332000000001</v>
+      </c>
+      <c r="AE75" s="6">
+        <v>0.92000000000000004</v>
+      </c>
       <c r="AF75" s="9"/>
-      <c r="AG75" s="5"/>
+      <c r="AG75" s="5">
+        <v>-428.39999999999998</v>
+      </c>
       <c r="AH75" s="10">
         <v>3</v>
       </c>
@@ -10610,7 +11027,9 @@
       <c r="AB77" s="8">
         <v>3.8953339999999996</v>
       </c>
-      <c r="AC77" s="8"/>
+      <c r="AC77" s="8">
+        <v>8.6689989999999995</v>
+      </c>
       <c r="AD77" s="8">
         <v>15.618333999999999</v>
       </c>
@@ -10735,7 +11154,9 @@
       <c r="AB78" s="8">
         <v>8.3797872340425545</v>
       </c>
-      <c r="AC78" s="8"/>
+      <c r="AC78" s="8">
+        <v>11.193262000000001</v>
+      </c>
       <c r="AD78" s="8">
         <v>19.150354255319147</v>
       </c>
@@ -10864,7 +11285,9 @@
       <c r="AB79" s="8">
         <v>12.465476785714285</v>
       </c>
-      <c r="AC79" s="8"/>
+      <c r="AC79" s="8">
+        <v>20.672658999999999</v>
+      </c>
       <c r="AD79" s="8">
         <v>27.014655172413793</v>
       </c>
@@ -10991,7 +11414,9 @@
       <c r="AB80" s="8">
         <v>11.218147777777776</v>
       </c>
-      <c r="AC80" s="8"/>
+      <c r="AC80" s="8">
+        <v>16.311005000000002</v>
+      </c>
       <c r="AD80" s="8">
         <v>25.944321978021978</v>
       </c>
@@ -11118,7 +11543,9 @@
       <c r="AB81" s="8">
         <v>7.6743041666666665</v>
       </c>
-      <c r="AC81" s="8"/>
+      <c r="AC81" s="8">
+        <v>12.218055</v>
+      </c>
       <c r="AD81" s="8">
         <v>19.177779166666667</v>
       </c>
@@ -11247,7 +11674,9 @@
       <c r="AB82" s="8">
         <v>5.4071032786885249</v>
       </c>
-      <c r="AC82" s="8"/>
+      <c r="AC82" s="8">
+        <v>9.4136600000000001</v>
+      </c>
       <c r="AD82" s="8">
         <v>16.336339344262296</v>
       </c>
@@ -11469,7 +11898,9 @@
       <c r="AB84" s="8">
         <v>5.8921775510204082</v>
       </c>
-      <c r="AC84" s="8"/>
+      <c r="AC84" s="8">
+        <v>13.370054</v>
+      </c>
       <c r="AD84" s="8">
         <v>19.375758181818181</v>
       </c>
@@ -11598,7 +12029,9 @@
       <c r="AB85" s="8">
         <v>26.894446666666667</v>
       </c>
-      <c r="AC85" s="8"/>
+      <c r="AC85" s="8">
+        <v>34.662962</v>
+      </c>
       <c r="AD85" s="8">
         <v>41.22222</v>
       </c>
@@ -11649,7 +12082,7 @@
         <v>19688</v>
       </c>
       <c r="B86" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C86" s="4">
         <v>44</v>
@@ -11685,25 +12118,59 @@
       <c t="s" r="N86" s="4">
         <v>52</v>
       </c>
-      <c r="O86" s="5"/>
-      <c r="P86" s="5"/>
-      <c r="Q86" s="6"/>
-      <c r="R86" s="7"/>
-      <c r="S86" s="6"/>
-      <c r="T86" s="6"/>
-      <c r="U86" s="6"/>
-      <c r="V86" s="6"/>
-      <c r="W86" s="6"/>
-      <c r="X86" s="8"/>
-      <c r="Y86" s="6"/>
-      <c r="Z86" s="6"/>
-      <c r="AA86" s="8"/>
-      <c r="AB86" s="8"/>
+      <c r="O86" s="5">
+        <v>10056.040000000001</v>
+      </c>
+      <c r="P86" s="5">
+        <v>10056.040000000001</v>
+      </c>
+      <c r="Q86" s="6">
+        <v>0.19103364632979281</v>
+      </c>
+      <c r="R86" s="7">
+        <v>99</v>
+      </c>
+      <c r="S86" s="6">
+        <v>0</v>
+      </c>
+      <c r="T86" s="6">
+        <v>0.32946450093675045</v>
+      </c>
+      <c r="U86" s="6">
+        <v>0.010601409700040969</v>
+      </c>
+      <c r="V86" s="6">
+        <v>0.012383303964582478</v>
+      </c>
+      <c r="W86" s="6">
+        <v>-0.003546425829650637</v>
+      </c>
+      <c r="X86" s="8">
+        <v>41.288405797101447</v>
+      </c>
+      <c r="Y86" s="6">
+        <v>0.40579710144927539</v>
+      </c>
+      <c r="Z86" s="6">
+        <v>0.53623188405797106</v>
+      </c>
+      <c r="AA86" s="8">
+        <v>12.948989898989899</v>
+      </c>
+      <c r="AB86" s="8">
+        <v>7.2873134328358207</v>
+      </c>
       <c r="AC86" s="8"/>
-      <c r="AD86" s="8"/>
-      <c r="AE86" s="6"/>
+      <c r="AD86" s="8">
+        <v>28.789613043478262</v>
+      </c>
+      <c r="AE86" s="6">
+        <v>0.13043478260869565</v>
+      </c>
       <c r="AF86" s="9"/>
-      <c r="AG86" s="5"/>
+      <c r="AG86" s="5">
+        <v>-118.8</v>
+      </c>
       <c r="AH86" s="10">
         <v>3</v>
       </c>
@@ -11822,7 +12289,9 @@
       <c r="AB87" s="8">
         <v>3.915685294117647</v>
       </c>
-      <c r="AC87" s="8"/>
+      <c r="AC87" s="8">
+        <v>6.8197510000000001</v>
+      </c>
       <c r="AD87" s="8">
         <v>12.504470731707318</v>
       </c>
@@ -11949,7 +12418,9 @@
       <c r="AB88" s="8">
         <v>7.0242418181818183</v>
       </c>
-      <c r="AC88" s="8"/>
+      <c r="AC88" s="8">
+        <v>11.688527000000001</v>
+      </c>
       <c r="AD88" s="8">
         <v>17.764880357142857</v>
       </c>
@@ -12093,7 +12564,7 @@
         <v>19694</v>
       </c>
       <c r="B90" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C90" s="4">
         <v>44</v>
@@ -12129,25 +12600,59 @@
       <c t="s" r="N90" s="4">
         <v>52</v>
       </c>
-      <c r="O90" s="5"/>
-      <c r="P90" s="5"/>
-      <c r="Q90" s="6"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="6"/>
-      <c r="T90" s="6"/>
-      <c r="U90" s="6"/>
-      <c r="V90" s="6"/>
-      <c r="W90" s="6"/>
-      <c r="X90" s="8"/>
-      <c r="Y90" s="6"/>
-      <c r="Z90" s="6"/>
-      <c r="AA90" s="8"/>
-      <c r="AB90" s="8"/>
+      <c r="O90" s="5">
+        <v>7605.3000000000002</v>
+      </c>
+      <c r="P90" s="5">
+        <v>7605.3000000000002</v>
+      </c>
+      <c r="Q90" s="6">
+        <v>0.24012666566656016</v>
+      </c>
+      <c r="R90" s="7">
+        <v>80</v>
+      </c>
+      <c r="S90" s="6">
+        <v>0.038961038961038863</v>
+      </c>
+      <c r="T90" s="6">
+        <v>-1.3945833300461519</v>
+      </c>
+      <c r="U90" s="6">
+        <v>-4.9454873049057886</v>
+      </c>
+      <c r="V90" s="6">
+        <v>0.028992741903672438</v>
+      </c>
+      <c r="W90" s="6">
+        <v>0.0094563659553206312</v>
+      </c>
+      <c r="X90" s="8">
+        <v>33.360801851851853</v>
+      </c>
+      <c r="Y90" s="6">
+        <v>0.1111111111111111</v>
+      </c>
+      <c r="Z90" s="6">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="AA90" s="8">
+        <v>7.8972912500000003</v>
+      </c>
+      <c r="AB90" s="8">
+        <v>15.317628846153847</v>
+      </c>
       <c r="AC90" s="8"/>
-      <c r="AD90" s="8"/>
-      <c r="AE90" s="6"/>
+      <c r="AD90" s="8">
+        <v>29.30462962962963</v>
+      </c>
+      <c r="AE90" s="6">
+        <v>0.61111111111111116</v>
+      </c>
       <c r="AF90" s="9"/>
-      <c r="AG90" s="5"/>
+      <c r="AG90" s="5">
+        <v>-476.16000000000003</v>
+      </c>
       <c r="AH90" s="10">
         <v>2</v>
       </c>
@@ -12266,7 +12771,9 @@
       <c r="AB91" s="8">
         <v>5.1729508196721312</v>
       </c>
-      <c r="AC91" s="8"/>
+      <c r="AC91" s="8">
+        <v>11.316071000000001</v>
+      </c>
       <c r="AD91" s="8">
         <v>17.951852380952381</v>
       </c>
@@ -12395,7 +12902,9 @@
       <c r="AB92" s="8">
         <v>5.3225499999999997</v>
       </c>
-      <c r="AC92" s="8"/>
+      <c r="AC92" s="8">
+        <v>12.368043999999999</v>
+      </c>
       <c r="AD92" s="8">
         <v>19.731480555555557</v>
       </c>
@@ -12522,7 +13031,9 @@
       <c r="AB93" s="8">
         <v>3.7201030927835053</v>
       </c>
-      <c r="AC93" s="8"/>
+      <c r="AC93" s="8">
+        <v>5.5388900000000003</v>
+      </c>
       <c r="AD93" s="8">
         <v>11.609393636363636</v>
       </c>
@@ -12649,7 +13160,9 @@
       <c r="AB94" s="8">
         <v>6.8673076923076923</v>
       </c>
-      <c r="AC94" s="8"/>
+      <c r="AC94" s="8">
+        <v>17.537709</v>
+      </c>
       <c r="AD94" s="8">
         <v>24.418965517241379</v>
       </c>
@@ -12871,7 +13384,9 @@
       <c r="AB96" s="8">
         <v>66.23595214285713</v>
       </c>
-      <c r="AC96" s="8"/>
+      <c r="AC96" s="8">
+        <v>73.378303000000002</v>
+      </c>
       <c r="AD96" s="8">
         <v>72.137277099236641</v>
       </c>
@@ -13000,7 +13515,9 @@
       <c r="AB97" s="8">
         <v>2.5034729166666669</v>
       </c>
-      <c r="AC97" s="8"/>
+      <c r="AC97" s="8">
+        <v>10.175907</v>
+      </c>
       <c r="AD97" s="8">
         <v>15.892156862745098</v>
       </c>
@@ -13129,7 +13646,9 @@
       <c r="AB98" s="8">
         <v>17.285771951219512</v>
       </c>
-      <c r="AC98" s="8"/>
+      <c r="AC98" s="8">
+        <v>22.081956000000002</v>
+      </c>
       <c r="AD98" s="8">
         <v>28.99044756097561</v>
       </c>
@@ -13258,7 +13777,9 @@
       <c r="AB99" s="8">
         <v>5.1115083333333331</v>
       </c>
-      <c r="AC99" s="8"/>
+      <c r="AC99" s="8">
+        <v>12.488292</v>
+      </c>
       <c r="AD99" s="8">
         <v>19.425000000000001</v>
       </c>
@@ -13387,7 +13908,9 @@
       <c r="AB100" s="8">
         <v>42.558470491803277</v>
       </c>
-      <c r="AC100" s="8"/>
+      <c r="AC100" s="8">
+        <v>49.208469000000001</v>
+      </c>
       <c r="AD100" s="8">
         <v>58.166119672131146</v>
       </c>
@@ -13514,7 +14037,9 @@
       <c r="AB101" s="8">
         <v>17.685896923076925</v>
       </c>
-      <c r="AC101" s="8"/>
+      <c r="AC101" s="8">
+        <v>20.530341</v>
+      </c>
       <c r="AD101" s="8">
         <v>27.072980303030306</v>
       </c>
@@ -13738,7 +14263,9 @@
       <c r="AB103" s="8">
         <v>3.7666666666666666</v>
       </c>
-      <c r="AC103" s="8"/>
+      <c r="AC103" s="8">
+        <v>10.256943</v>
+      </c>
       <c r="AD103" s="8">
         <v>16.095289130434782</v>
       </c>
@@ -13867,7 +14394,9 @@
       <c r="AB104" s="8">
         <v>4.6445360655737709</v>
       </c>
-      <c r="AC104" s="8"/>
+      <c r="AC104" s="8">
+        <v>9.695055</v>
+      </c>
       <c r="AD104" s="8">
         <v>17.992592063492065</v>
       </c>
@@ -13994,7 +14523,9 @@
       <c r="AB105" s="8">
         <v>51.708332142857145</v>
       </c>
-      <c r="AC105" s="8"/>
+      <c r="AC105" s="8">
+        <v>79.004431999999994</v>
+      </c>
       <c r="AD105" s="8">
         <v>45.965000000000003</v>
       </c>
@@ -14123,7 +14654,9 @@
       <c r="AB106" s="8">
         <v>0.81190357142857139</v>
       </c>
-      <c r="AC106" s="8"/>
+      <c r="AC106" s="8">
+        <v>8.4871909999999993</v>
+      </c>
       <c r="AD106" s="8">
         <v>15.579167857142858</v>
       </c>
@@ -14252,7 +14785,9 @@
       <c r="AB107" s="8">
         <v>7.8933327272727274</v>
       </c>
-      <c r="AC107" s="8"/>
+      <c r="AC107" s="8">
+        <v>14.33212</v>
+      </c>
       <c r="AD107" s="8">
         <v>21.278787272727271</v>
       </c>
@@ -14396,7 +14931,7 @@
         <v>19730</v>
       </c>
       <c r="B109" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C109" s="4">
         <v>44</v>
@@ -14430,25 +14965,59 @@
       <c t="s" r="N109" s="4">
         <v>52</v>
       </c>
-      <c r="O109" s="5"/>
-      <c r="P109" s="5"/>
-      <c r="Q109" s="6"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="6"/>
-      <c r="T109" s="6"/>
-      <c r="U109" s="6"/>
-      <c r="V109" s="6"/>
-      <c r="W109" s="6"/>
-      <c r="X109" s="8"/>
-      <c r="Y109" s="6"/>
-      <c r="Z109" s="6"/>
-      <c r="AA109" s="8"/>
-      <c r="AB109" s="8"/>
+      <c r="O109" s="5">
+        <v>10766.41</v>
+      </c>
+      <c r="P109" s="5">
+        <v>10766.41</v>
+      </c>
+      <c r="Q109" s="6">
+        <v>0.1508771817303336</v>
+      </c>
+      <c r="R109" s="7">
+        <v>114</v>
+      </c>
+      <c r="S109" s="6">
+        <v>0.085714285714285632</v>
+      </c>
+      <c r="T109" s="6">
+        <v>-0.0091023841744834171</v>
+      </c>
+      <c r="U109" s="6">
+        <v>-0.34543362179222231</v>
+      </c>
+      <c r="V109" s="6">
+        <v>0.056226216538288999</v>
+      </c>
+      <c r="W109" s="6">
+        <v>0.034015470337837771</v>
+      </c>
+      <c r="X109" s="8">
+        <v>26.257472413793103</v>
+      </c>
+      <c r="Y109" s="6">
+        <v>0.51724137931034486</v>
+      </c>
+      <c r="Z109" s="6">
+        <v>0.034482758620689655</v>
+      </c>
+      <c r="AA109" s="8">
+        <v>5.0401452173913048</v>
+      </c>
+      <c r="AB109" s="8">
+        <v>8.2580448275862075</v>
+      </c>
       <c r="AC109" s="8"/>
-      <c r="AD109" s="8"/>
-      <c r="AE109" s="6"/>
+      <c r="AD109" s="8">
+        <v>21.538506896551727</v>
+      </c>
+      <c r="AE109" s="6">
+        <v>0.58620689655172409</v>
+      </c>
       <c r="AF109" s="9"/>
-      <c r="AG109" s="5"/>
+      <c r="AG109" s="5">
+        <v>-88.799999999999997</v>
+      </c>
       <c r="AH109" s="10">
         <v>2</v>
       </c>
@@ -14660,7 +15229,9 @@
       <c r="AB111" s="8">
         <v>0.58645625000000001</v>
       </c>
-      <c r="AC111" s="8"/>
+      <c r="AC111" s="8">
+        <v>7.7291660000000002</v>
+      </c>
       <c r="AD111" s="8">
         <v>14.690625000000001</v>
       </c>
@@ -14880,7 +15451,9 @@
       <c r="AB113" s="8">
         <v>1.7</v>
       </c>
-      <c r="AC113" s="8"/>
+      <c r="AC113" s="8">
+        <v>3.9698709999999999</v>
+      </c>
       <c r="AD113" s="8">
         <v>13.479807692307693</v>
       </c>
@@ -15009,7 +15582,9 @@
       <c r="AB114" s="8">
         <v>7.1232645833333335</v>
       </c>
-      <c r="AC114" s="8"/>
+      <c r="AC114" s="8">
+        <v>12.545698</v>
+      </c>
       <c r="AD114" s="8">
         <v>20.064</v>
       </c>
@@ -15138,7 +15713,9 @@
       <c r="AB115" s="8">
         <v>4.1922233333333336</v>
       </c>
-      <c r="AC115" s="8"/>
+      <c r="AC115" s="8">
+        <v>7.5556619999999999</v>
+      </c>
       <c r="AD115" s="8">
         <v>15.297848387096774</v>
       </c>
@@ -15360,7 +15937,9 @@
       <c r="AB117" s="8">
         <v>19.337571186440677</v>
       </c>
-      <c r="AC117" s="8"/>
+      <c r="AC117" s="8">
+        <v>26.394821</v>
+      </c>
       <c r="AD117" s="8">
         <v>20.878533599999997</v>
       </c>
@@ -15489,7 +16068,9 @@
       <c r="AB118" s="8">
         <v>5.8281738095238094</v>
       </c>
-      <c r="AC118" s="8"/>
+      <c r="AC118" s="8">
+        <v>12.789285</v>
+      </c>
       <c r="AD118" s="8">
         <v>18.478818749999999</v>
       </c>
@@ -15618,7 +16199,9 @@
       <c r="AB119" s="8">
         <v>4.7519607843137255</v>
       </c>
-      <c r="AC119" s="8"/>
+      <c r="AC119" s="8">
+        <v>8.4967310000000005</v>
+      </c>
       <c r="AD119" s="8">
         <v>15.448692156862744</v>
       </c>
@@ -15745,7 +16328,9 @@
       <c r="AB120" s="8">
         <v>17.459322033898303</v>
       </c>
-      <c r="AC120" s="8"/>
+      <c r="AC120" s="8">
+        <v>23.764599</v>
+      </c>
       <c r="AD120" s="8">
         <v>31.699435593220336</v>
       </c>
@@ -15872,7 +16457,9 @@
       <c r="AB121" s="8">
         <v>4.8614562499999998</v>
       </c>
-      <c r="AC121" s="8"/>
+      <c r="AC121" s="8">
+        <v>10.790623999999999</v>
+      </c>
       <c r="AD121" s="8">
         <v>18.683331249999998</v>
       </c>
@@ -16001,7 +16588,9 @@
       <c r="AB122" s="8">
         <v>6.1734746478873239</v>
       </c>
-      <c r="AC122" s="8"/>
+      <c r="AC122" s="8">
+        <v>9.9621399999999998</v>
+      </c>
       <c r="AD122" s="8">
         <v>16.8666661971831</v>
       </c>
@@ -16130,7 +16719,9 @@
       <c r="AB123" s="8">
         <v>5.1769230769230772</v>
       </c>
-      <c r="AC123" s="8"/>
+      <c r="AC123" s="8">
+        <v>7.9909319999999999</v>
+      </c>
       <c r="AD123" s="8">
         <v>15.80707121212121</v>
       </c>
@@ -16255,7 +16846,9 @@
       <c r="AB124" s="8">
         <v>7.1537000000000006</v>
       </c>
-      <c r="AC124" s="8"/>
+      <c r="AC124" s="8">
+        <v>10.546295000000001</v>
+      </c>
       <c r="AD124" s="8">
         <v>18.501855555555554</v>
       </c>
@@ -16384,7 +16977,9 @@
       <c r="AB125" s="8">
         <v>4.9722218390804596</v>
       </c>
-      <c r="AC125" s="8"/>
+      <c r="AC125" s="8">
+        <v>7.9527479999999997</v>
+      </c>
       <c r="AD125" s="8">
         <v>15.418681318681317</v>
       </c>
@@ -16435,7 +17030,7 @@
         <v>19759</v>
       </c>
       <c r="B126" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C126" s="4">
         <v>44</v>
@@ -16471,25 +17066,59 @@
       <c t="s" r="N126" s="4">
         <v>52</v>
       </c>
-      <c r="O126" s="5"/>
-      <c r="P126" s="5"/>
-      <c r="Q126" s="6"/>
-      <c r="R126" s="7"/>
-      <c r="S126" s="6"/>
-      <c r="T126" s="6"/>
-      <c r="U126" s="6"/>
-      <c r="V126" s="6"/>
-      <c r="W126" s="6"/>
-      <c r="X126" s="8"/>
-      <c r="Y126" s="6"/>
-      <c r="Z126" s="6"/>
-      <c r="AA126" s="8"/>
-      <c r="AB126" s="8"/>
+      <c r="O126" s="5">
+        <v>4379.71</v>
+      </c>
+      <c r="P126" s="5">
+        <v>4379.71</v>
+      </c>
+      <c r="Q126" s="6">
+        <v>-0.31588730449560531</v>
+      </c>
+      <c r="R126" s="7">
+        <v>49</v>
+      </c>
+      <c r="S126" s="6">
+        <v>-0.4731182795698925</v>
+      </c>
+      <c r="T126" s="6">
+        <v>0</v>
+      </c>
+      <c r="U126" s="6">
+        <v>-0.2569599357035055</v>
+      </c>
+      <c r="V126" s="6">
+        <v>0.031681549691646251</v>
+      </c>
+      <c r="W126" s="6">
+        <v>0.018676122391665204</v>
+      </c>
+      <c r="X126" s="8">
+        <v>42.794087096774192</v>
+      </c>
+      <c r="Y126" s="6">
+        <v>0.38709677419354838</v>
+      </c>
+      <c r="Z126" s="6">
+        <v>0.54838709677419351</v>
+      </c>
+      <c r="AA126" s="8">
+        <v>7.7217693877551019</v>
+      </c>
+      <c r="AB126" s="8">
+        <v>19.246109999999998</v>
+      </c>
       <c r="AC126" s="8"/>
-      <c r="AD126" s="8"/>
-      <c r="AE126" s="6"/>
+      <c r="AD126" s="8">
+        <v>32.736022580645162</v>
+      </c>
+      <c r="AE126" s="6">
+        <v>0.096774193548387094</v>
+      </c>
       <c r="AF126" s="9"/>
-      <c r="AG126" s="5"/>
+      <c r="AG126" s="5">
+        <v>0</v>
+      </c>
       <c r="AH126" s="10">
         <v>2</v>
       </c>
@@ -16608,7 +17237,9 @@
       <c r="AB127" s="8">
         <v>11.901040625</v>
       </c>
-      <c r="AC127" s="8"/>
+      <c r="AC127" s="8">
+        <v>20.986457000000001</v>
+      </c>
       <c r="AD127" s="8">
         <v>30.847396875000001</v>
       </c>
@@ -16737,7 +17368,9 @@
       <c r="AB128" s="8">
         <v>3.1878818181818178</v>
       </c>
-      <c r="AC128" s="8"/>
+      <c r="AC128" s="8">
+        <v>11.585497</v>
+      </c>
       <c r="AD128" s="8">
         <v>16.265553333333333</v>
       </c>
@@ -16866,7 +17499,9 @@
       <c r="AB129" s="8">
         <v>36.960970886075955</v>
       </c>
-      <c r="AC129" s="8"/>
+      <c r="AC129" s="8">
+        <v>42.656595000000003</v>
+      </c>
       <c r="AD129" s="8">
         <v>49.030416250000002</v>
       </c>
@@ -16995,7 +17630,9 @@
       <c r="AB130" s="8">
         <v>10.989923255813954</v>
       </c>
-      <c r="AC130" s="8"/>
+      <c r="AC130" s="8">
+        <v>13.497963</v>
+      </c>
       <c r="AD130" s="8">
         <v>19.218115217391304</v>
       </c>
@@ -17122,7 +17759,9 @@
       <c r="AB131" s="8">
         <v>16.581882608695654</v>
       </c>
-      <c r="AC131" s="8"/>
+      <c r="AC131" s="8">
+        <v>23.860869000000001</v>
+      </c>
       <c r="AD131" s="8">
         <v>29.722220833333335</v>
       </c>
@@ -17251,7 +17890,9 @@
       <c r="AB132" s="8">
         <v>10.221243523316062</v>
       </c>
-      <c r="AC132" s="8"/>
+      <c r="AC132" s="8">
+        <v>41.131141</v>
+      </c>
       <c r="AD132" s="8">
         <v>46.79081632653061</v>
       </c>
@@ -17380,7 +18021,9 @@
       <c r="AB133" s="8">
         <v>15.961110256410256</v>
       </c>
-      <c r="AC133" s="8"/>
+      <c r="AC133" s="8">
+        <v>21.946527</v>
+      </c>
       <c r="AD133" s="8">
         <v>28.918802564102563</v>
       </c>
@@ -17509,7 +18152,9 @@
       <c r="AB134" s="8">
         <v>9.9620388888888893</v>
       </c>
-      <c r="AC134" s="8"/>
+      <c r="AC134" s="8">
+        <v>17.407406999999999</v>
+      </c>
       <c r="AD134" s="8">
         <v>24.645372222222221</v>
       </c>
@@ -17638,7 +18283,9 @@
       <c r="AB135" s="8">
         <v>2.947222222222222</v>
       </c>
-      <c r="AC135" s="8"/>
+      <c r="AC135" s="8">
+        <v>6.3638880000000002</v>
+      </c>
       <c r="AD135" s="8">
         <v>13.32685</v>
       </c>
@@ -17767,7 +18414,9 @@
       <c r="AB136" s="8">
         <v>18.458332142857142</v>
       </c>
-      <c r="AC136" s="8"/>
+      <c r="AC136" s="8">
+        <v>24.427379999999999</v>
+      </c>
       <c r="AD136" s="8">
         <v>31.264285714285712</v>
       </c>
@@ -17894,7 +18543,9 @@
       <c r="AB137" s="8">
         <v>8.5616699999999994</v>
       </c>
-      <c r="AC137" s="8"/>
+      <c r="AC137" s="8">
+        <v>15.879999</v>
+      </c>
       <c r="AD137" s="8">
         <v>22.805</v>
       </c>
@@ -18021,7 +18672,9 @@
       <c r="AB138" s="8">
         <v>9.2682830303030297</v>
       </c>
-      <c r="AC138" s="8"/>
+      <c r="AC138" s="8">
+        <v>16.272203000000001</v>
+      </c>
       <c r="AD138" s="8">
         <v>22.644082840236685</v>
       </c>
@@ -18150,7 +18803,9 @@
       <c r="AB139" s="8">
         <v>4.870967741935484</v>
       </c>
-      <c r="AC139" s="8"/>
+      <c r="AC139" s="8">
+        <v>7.0128579999999996</v>
+      </c>
       <c r="AD139" s="8">
         <v>11.713513513513513</v>
       </c>
@@ -18467,7 +19122,9 @@
       <c r="AB142" s="8">
         <v>9.9417910447761191</v>
       </c>
-      <c r="AC142" s="8"/>
+      <c r="AC142" s="8">
+        <v>16.039244</v>
+      </c>
       <c r="AD142" s="8">
         <v>24.218332857142858</v>
       </c>
@@ -18594,7 +19251,9 @@
       <c r="AB143" s="8">
         <v>8.2333333333333343</v>
       </c>
-      <c r="AC143" s="8"/>
+      <c r="AC143" s="8">
+        <v>14.538513</v>
+      </c>
       <c r="AD143" s="8">
         <v>21.952083333333334</v>
       </c>
@@ -18723,7 +19382,9 @@
       <c r="AB144" s="8">
         <v>1.0983050847457627</v>
       </c>
-      <c r="AC144" s="8"/>
+      <c r="AC144" s="8">
+        <v>3.5721509999999999</v>
+      </c>
       <c r="AD144" s="8">
         <v>10.235156249999999</v>
       </c>
@@ -18852,7 +19513,9 @@
       <c r="AB145" s="8">
         <v>14.548486363636364</v>
       </c>
-      <c r="AC145" s="8"/>
+      <c r="AC145" s="8">
+        <v>21.848096000000002</v>
+      </c>
       <c r="AD145" s="8">
         <v>15.763888095238096</v>
       </c>
@@ -18981,7 +19644,9 @@
       <c r="AB146" s="8">
         <v>5.7284615384615387</v>
       </c>
-      <c r="AC146" s="8"/>
+      <c r="AC146" s="8">
+        <v>14.853460999999999</v>
+      </c>
       <c r="AD146" s="8">
         <v>20.693939393939392</v>
       </c>
@@ -19110,7 +19775,9 @@
       <c r="AB147" s="8">
         <v>3.4489893939393936</v>
       </c>
-      <c r="AC147" s="8"/>
+      <c r="AC147" s="8">
+        <v>15.406948999999999</v>
+      </c>
       <c r="AD147" s="8">
         <v>21.960198507462685</v>
       </c>
@@ -19241,7 +19908,9 @@
       <c r="AB148" s="8">
         <v>42.920192307692304</v>
       </c>
-      <c r="AC148" s="8"/>
+      <c r="AC148" s="8">
+        <v>51.182253000000003</v>
+      </c>
       <c r="AD148" s="8">
         <v>46.813503649635038</v>
       </c>
@@ -19292,7 +19961,7 @@
         <v>19817</v>
       </c>
       <c r="B149" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C149" s="4">
         <v>44</v>
@@ -19328,25 +19997,59 @@
       <c t="s" r="N149" s="4">
         <v>52</v>
       </c>
-      <c r="O149" s="5"/>
-      <c r="P149" s="5"/>
-      <c r="Q149" s="6"/>
-      <c r="R149" s="7"/>
-      <c r="S149" s="6"/>
-      <c r="T149" s="6"/>
-      <c r="U149" s="6"/>
-      <c r="V149" s="6"/>
-      <c r="W149" s="6"/>
-      <c r="X149" s="8"/>
-      <c r="Y149" s="6"/>
-      <c r="Z149" s="6"/>
-      <c r="AA149" s="8"/>
-      <c r="AB149" s="8"/>
+      <c r="O149" s="5">
+        <v>9984.2399999999998</v>
+      </c>
+      <c r="P149" s="5">
+        <v>9984.2399999999998</v>
+      </c>
+      <c r="Q149" s="6">
+        <v>-0.072211334472597755</v>
+      </c>
+      <c r="R149" s="7">
+        <v>129</v>
+      </c>
+      <c r="S149" s="6">
+        <v>0.20560747663551404</v>
+      </c>
+      <c r="T149" s="6">
+        <v>0.34696591828722062</v>
+      </c>
+      <c r="U149" s="6">
+        <v>0.024330444780974816</v>
+      </c>
+      <c r="V149" s="6">
+        <v>0.040742410038220232</v>
+      </c>
+      <c r="W149" s="6">
+        <v>0.0072946964415919486</v>
+      </c>
+      <c r="X149" s="8">
+        <v>127.50498547008547</v>
+      </c>
+      <c r="Y149" s="6">
+        <v>0.033898305084745763</v>
+      </c>
+      <c r="Z149" s="6">
+        <v>0.83760683760683763</v>
+      </c>
+      <c r="AA149" s="8">
+        <v>24.886466165413534</v>
+      </c>
+      <c r="AB149" s="8">
+        <v>62.44140927835052</v>
+      </c>
       <c r="AC149" s="8"/>
-      <c r="AD149" s="8"/>
-      <c r="AE149" s="6"/>
+      <c r="AD149" s="8">
+        <v>77.362451724137927</v>
+      </c>
+      <c r="AE149" s="6">
+        <v>0.068376068376068383</v>
+      </c>
       <c r="AF149" s="9"/>
-      <c r="AG149" s="5"/>
+      <c r="AG149" s="5">
+        <v>0</v>
+      </c>
       <c r="AH149" s="10">
         <v>2</v>
       </c>
@@ -19463,7 +20166,9 @@
       <c r="AB150" s="8">
         <v>3.4934782608695651</v>
       </c>
-      <c r="AC150" s="8"/>
+      <c r="AC150" s="8">
+        <v>9.2495999999999992</v>
+      </c>
       <c r="AD150" s="8">
         <v>15.755442857142857</v>
       </c>
@@ -19691,7 +20396,9 @@
       <c r="AB152" s="8">
         <v>4.7148148148148143</v>
       </c>
-      <c r="AC152" s="8"/>
+      <c r="AC152" s="8">
+        <v>9.8796280000000003</v>
+      </c>
       <c r="AD152" s="8">
         <v>16.810801851851853</v>
       </c>
@@ -19820,7 +20527,9 @@
       <c r="AB153" s="8">
         <v>13.546354166666667</v>
       </c>
-      <c r="AC153" s="8"/>
+      <c r="AC153" s="8">
+        <v>20.493749000000001</v>
+      </c>
       <c r="AD153" s="8">
         <v>28.402604166666666</v>
       </c>
@@ -19949,7 +20658,9 @@
       <c r="AB154" s="8">
         <v>10.142130555555555</v>
       </c>
-      <c r="AC154" s="8"/>
+      <c r="AC154" s="8">
+        <v>14.644380999999999</v>
+      </c>
       <c r="AD154" s="8">
         <v>23.226127027027029</v>
       </c>
@@ -20076,7 +20787,9 @@
       <c r="AB155" s="8">
         <v>3.7664604938271604</v>
       </c>
-      <c r="AC155" s="8"/>
+      <c r="AC155" s="8">
+        <v>6.8277760000000001</v>
+      </c>
       <c r="AD155" s="8">
         <v>12.904527160493826</v>
       </c>
@@ -20205,7 +20918,9 @@
       <c r="AB156" s="8">
         <v>5.9021499999999998</v>
       </c>
-      <c r="AC156" s="8"/>
+      <c r="AC156" s="8">
+        <v>11.811826999999999</v>
+      </c>
       <c r="AD156" s="8">
         <v>18.737096774193549</v>
       </c>
@@ -20496,7 +21211,9 @@
       <c r="Z159" s="6"/>
       <c r="AA159" s="8"/>
       <c r="AB159" s="8"/>
-      <c r="AC159" s="8"/>
+      <c r="AC159" s="8">
+        <v>29.230885000000001</v>
+      </c>
       <c r="AD159" s="8"/>
       <c r="AE159" s="6"/>
       <c r="AF159" s="9"/>
@@ -20615,7 +21332,9 @@
       <c r="AB160" s="8">
         <v>15.019270833333332</v>
       </c>
-      <c r="AC160" s="8"/>
+      <c r="AC160" s="8">
+        <v>22.396006</v>
+      </c>
       <c r="AD160" s="8">
         <v>29.300000000000001</v>
       </c>
@@ -20791,7 +21510,7 @@
         <v>19872</v>
       </c>
       <c r="B162" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C162" s="4">
         <v>44</v>
@@ -20827,25 +21546,59 @@
       <c t="s" r="N162" s="4">
         <v>52</v>
       </c>
-      <c r="O162" s="5"/>
-      <c r="P162" s="5"/>
-      <c r="Q162" s="6"/>
-      <c r="R162" s="7"/>
-      <c r="S162" s="6"/>
-      <c r="T162" s="6"/>
-      <c r="U162" s="6"/>
-      <c r="V162" s="6"/>
-      <c r="W162" s="6"/>
-      <c r="X162" s="8"/>
-      <c r="Y162" s="6"/>
-      <c r="Z162" s="6"/>
-      <c r="AA162" s="8"/>
-      <c r="AB162" s="8"/>
+      <c r="O162" s="5">
+        <v>10386.83</v>
+      </c>
+      <c r="P162" s="5">
+        <v>10386.83</v>
+      </c>
+      <c r="Q162" s="6">
+        <v>0.01325634527175068</v>
+      </c>
+      <c r="R162" s="7">
+        <v>101</v>
+      </c>
+      <c r="S162" s="6">
+        <v>-0.11403508771929827</v>
+      </c>
+      <c r="T162" s="6">
+        <v>0.27237973472175819</v>
+      </c>
+      <c r="U162" s="6">
+        <v>-0.011891789891622371</v>
+      </c>
+      <c r="V162" s="6">
+        <v>0.0058467309082751908</v>
+      </c>
+      <c r="W162" s="6">
+        <v>-0.002983682220658276</v>
+      </c>
+      <c r="X162" s="8">
+        <v>29.062627272727273</v>
+      </c>
+      <c r="Y162" s="6">
+        <v>0.5757575757575758</v>
+      </c>
+      <c r="Z162" s="6">
+        <v>0.030303030303030304</v>
+      </c>
+      <c r="AA162" s="8">
+        <v>8.9496567010309285</v>
+      </c>
+      <c r="AB162" s="8">
+        <v>3.5963531249999998</v>
+      </c>
       <c r="AC162" s="8"/>
-      <c r="AD162" s="8"/>
-      <c r="AE162" s="6"/>
+      <c r="AD162" s="8">
+        <v>21.324242424242424</v>
+      </c>
+      <c r="AE162" s="6">
+        <v>0.54545454545454541</v>
+      </c>
       <c r="AF162" s="9"/>
-      <c r="AG162" s="5"/>
+      <c r="AG162" s="5">
+        <v>-612.20000000000005</v>
+      </c>
       <c r="AH162" s="10">
         <v>2</v>
       </c>
@@ -20964,7 +21717,9 @@
       <c r="AB163" s="8">
         <v>9.0407122137404574</v>
       </c>
-      <c r="AC163" s="8"/>
+      <c r="AC163" s="8">
+        <v>12.991447000000001</v>
+      </c>
       <c r="AD163" s="8">
         <v>20.135265942028987</v>
       </c>
@@ -21093,7 +21848,9 @@
       <c r="AB164" s="8">
         <v>4.6916656249999997</v>
       </c>
-      <c r="AC164" s="8"/>
+      <c r="AC164" s="8">
+        <v>9.4955739999999995</v>
+      </c>
       <c r="AD164" s="8">
         <v>14.367520512820514</v>
       </c>
@@ -21317,7 +22074,9 @@
       <c r="AB166" s="8">
         <v>11.886666666666667</v>
       </c>
-      <c r="AC166" s="8"/>
+      <c r="AC166" s="8">
+        <v>15.288888</v>
+      </c>
       <c r="AD166" s="8">
         <v>22.197223333333334</v>
       </c>
@@ -21446,7 +22205,9 @@
       <c r="AB167" s="8">
         <v>5.8905097222222222</v>
       </c>
-      <c r="AC167" s="8"/>
+      <c r="AC167" s="8">
+        <v>8.7763190000000009</v>
+      </c>
       <c r="AD167" s="8">
         <v>14.762837837837839</v>
       </c>
@@ -21575,7 +22336,9 @@
       <c r="AB168" s="8">
         <v>4.2356719298245613</v>
       </c>
-      <c r="AC168" s="8"/>
+      <c r="AC168" s="8">
+        <v>6.865672</v>
+      </c>
       <c r="AD168" s="8">
         <v>13.46864406779661</v>
       </c>
@@ -21704,7 +22467,9 @@
       <c r="AB169" s="8">
         <v>4.5059754716981129</v>
       </c>
-      <c r="AC169" s="8"/>
+      <c r="AC169" s="8">
+        <v>12.603735</v>
+      </c>
       <c r="AD169" s="8">
         <v>17.788131818181817</v>
       </c>
@@ -21833,7 +22598,9 @@
       <c r="AB170" s="8">
         <v>5.6495029850746272</v>
       </c>
-      <c r="AC170" s="8"/>
+      <c r="AC170" s="8">
+        <v>15.866168</v>
+      </c>
       <c r="AD170" s="8">
         <v>21.976577027027027</v>
       </c>
@@ -21962,7 +22729,9 @@
       <c r="AB171" s="8">
         <v>3.1697183098591553</v>
       </c>
-      <c r="AC171" s="8"/>
+      <c r="AC171" s="8">
+        <v>10.005868</v>
+      </c>
       <c r="AD171" s="8">
         <v>16.928873239436619</v>
       </c>
@@ -22091,7 +22860,9 @@
       <c r="AB172" s="8">
         <v>6.5532925925925918</v>
       </c>
-      <c r="AC172" s="8"/>
+      <c r="AC172" s="8">
+        <v>9.8512339999999998</v>
+      </c>
       <c r="AD172" s="8">
         <v>16.80967037037037</v>
       </c>
@@ -22220,7 +22991,9 @@
       <c r="AB173" s="8">
         <v>8.0061099999999996</v>
       </c>
-      <c r="AC173" s="8"/>
+      <c r="AC173" s="8">
+        <v>14.82992</v>
+      </c>
       <c r="AD173" s="8">
         <v>17.484014285714284</v>
       </c>
@@ -22349,7 +23122,9 @@
       <c r="AB174" s="8">
         <v>3.6132530120481925</v>
       </c>
-      <c r="AC174" s="8"/>
+      <c r="AC174" s="8">
+        <v>8.9967839999999999</v>
+      </c>
       <c r="AD174" s="8">
         <v>15.874404761904762</v>
       </c>
@@ -22400,7 +23175,7 @@
         <v>19897</v>
       </c>
       <c r="B175" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C175" s="4">
         <v>44</v>
@@ -22436,25 +23211,59 @@
       <c t="s" r="N175" s="4">
         <v>52</v>
       </c>
-      <c r="O175" s="5"/>
-      <c r="P175" s="5"/>
-      <c r="Q175" s="6"/>
-      <c r="R175" s="7"/>
-      <c r="S175" s="6"/>
-      <c r="T175" s="6"/>
-      <c r="U175" s="6"/>
-      <c r="V175" s="6"/>
-      <c r="W175" s="6"/>
-      <c r="X175" s="8"/>
-      <c r="Y175" s="6"/>
-      <c r="Z175" s="6"/>
-      <c r="AA175" s="8"/>
-      <c r="AB175" s="8"/>
+      <c r="O175" s="5">
+        <v>4853.4899999999998</v>
+      </c>
+      <c r="P175" s="5">
+        <v>4853.4899999999998</v>
+      </c>
+      <c r="Q175" s="6">
+        <v>-0.0050694720615307443</v>
+      </c>
+      <c r="R175" s="7">
+        <v>68</v>
+      </c>
+      <c r="S175" s="6">
+        <v>-0.014492753623188359</v>
+      </c>
+      <c r="T175" s="6">
+        <v>0.19209370988711216</v>
+      </c>
+      <c r="U175" s="6">
+        <v>-0.17912370273761768</v>
+      </c>
+      <c r="V175" s="6">
+        <v>0.021949463169801522</v>
+      </c>
+      <c r="W175" s="6">
+        <v>-0.010256227992640348</v>
+      </c>
+      <c r="X175" s="8">
+        <v>28.845714285714287</v>
+      </c>
+      <c r="Y175" s="6">
+        <v>0.77142857142857146</v>
+      </c>
+      <c r="Z175" s="6">
+        <v>0.028571428571428571</v>
+      </c>
+      <c r="AA175" s="8">
+        <v>7.505290476190476</v>
+      </c>
+      <c r="AB175" s="8">
+        <v>3.0247484848484847</v>
+      </c>
       <c r="AC175" s="8"/>
-      <c r="AD175" s="8"/>
-      <c r="AE175" s="6"/>
+      <c r="AD175" s="8">
+        <v>18.05095142857143</v>
+      </c>
+      <c r="AE175" s="6">
+        <v>0.5714285714285714</v>
+      </c>
       <c r="AF175" s="9"/>
-      <c r="AG175" s="5"/>
+      <c r="AG175" s="5">
+        <v>-378.69999999999999</v>
+      </c>
       <c r="AH175" s="10">
         <v>2</v>
       </c>
@@ -22495,7 +23304,7 @@
         <v>19898</v>
       </c>
       <c r="B176" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C176" s="4">
         <v>44</v>
@@ -22529,25 +23338,55 @@
       <c t="s" r="N176" s="4">
         <v>52</v>
       </c>
-      <c r="O176" s="5"/>
-      <c r="P176" s="5"/>
+      <c r="O176" s="5">
+        <v>2829.8000000000002</v>
+      </c>
+      <c r="P176" s="5">
+        <v>2829.8000000000002</v>
+      </c>
       <c r="Q176" s="6"/>
-      <c r="R176" s="7"/>
+      <c r="R176" s="7">
+        <v>31</v>
+      </c>
       <c r="S176" s="6"/>
-      <c r="T176" s="6"/>
-      <c r="U176" s="6"/>
-      <c r="V176" s="6"/>
-      <c r="W176" s="6"/>
-      <c r="X176" s="8"/>
-      <c r="Y176" s="6"/>
-      <c r="Z176" s="6"/>
-      <c r="AA176" s="8"/>
-      <c r="AB176" s="8"/>
+      <c r="T176" s="6">
+        <v>0.0085624425754470268</v>
+      </c>
+      <c r="U176" s="6">
+        <v>-0.30145946710014843</v>
+      </c>
+      <c r="V176" s="6">
+        <v>0.11514082267298041</v>
+      </c>
+      <c r="W176" s="6">
+        <v>0.073318079016184895</v>
+      </c>
+      <c r="X176" s="8">
+        <v>25.791668749999999</v>
+      </c>
+      <c r="Y176" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z176" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA176" s="8">
+        <v>2.9421875000000002</v>
+      </c>
+      <c r="AB176" s="8">
+        <v>7.8260437500000002</v>
+      </c>
       <c r="AC176" s="8"/>
-      <c r="AD176" s="8"/>
-      <c r="AE176" s="6"/>
+      <c r="AD176" s="8">
+        <v>17.819793749999999</v>
+      </c>
+      <c r="AE176" s="6">
+        <v>0.6875</v>
+      </c>
       <c r="AF176" s="9"/>
-      <c r="AG176" s="5"/>
+      <c r="AG176" s="5">
+        <v>0</v>
+      </c>
       <c r="AH176" s="10">
         <v>3</v>
       </c>
@@ -22666,7 +23505,9 @@
       <c r="AB177" s="8">
         <v>2.5039235294117645</v>
       </c>
-      <c r="AC177" s="8"/>
+      <c r="AC177" s="8">
+        <v>6.031371</v>
+      </c>
       <c r="AD177" s="8">
         <v>12.978429411764706</v>
       </c>
@@ -22795,7 +23636,9 @@
       <c r="AB178" s="8">
         <v>3.4172833333333332</v>
       </c>
-      <c r="AC178" s="8"/>
+      <c r="AC178" s="8">
+        <v>7.7454640000000001</v>
+      </c>
       <c r="AD178" s="8">
         <v>14.575758181818182</v>
       </c>
@@ -22922,7 +23765,9 @@
       <c r="AB179" s="8">
         <v>1.7852459016393443</v>
       </c>
-      <c r="AC179" s="8"/>
+      <c r="AC179" s="8">
+        <v>5.7797799999999997</v>
+      </c>
       <c r="AD179" s="8">
         <v>12.723224590163936</v>
       </c>
@@ -22971,7 +23816,7 @@
         <v>19908</v>
       </c>
       <c r="B180" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C180" s="4">
         <v>44</v>
@@ -23007,25 +23852,59 @@
       <c t="s" r="N180" s="4">
         <v>52</v>
       </c>
-      <c r="O180" s="5"/>
-      <c r="P180" s="5"/>
-      <c r="Q180" s="6"/>
-      <c r="R180" s="7"/>
-      <c r="S180" s="6"/>
-      <c r="T180" s="6"/>
-      <c r="U180" s="6"/>
-      <c r="V180" s="6"/>
-      <c r="W180" s="6"/>
-      <c r="X180" s="8"/>
-      <c r="Y180" s="6"/>
-      <c r="Z180" s="6"/>
-      <c r="AA180" s="8"/>
-      <c r="AB180" s="8"/>
+      <c r="O180" s="5">
+        <v>3078.4499999999998</v>
+      </c>
+      <c r="P180" s="5">
+        <v>3078.4499999999998</v>
+      </c>
+      <c r="Q180" s="6">
+        <v>-0.51068452825630151</v>
+      </c>
+      <c r="R180" s="7">
+        <v>40</v>
+      </c>
+      <c r="S180" s="6">
+        <v>-0.43661971830985913</v>
+      </c>
+      <c r="T180" s="6">
+        <v>0</v>
+      </c>
+      <c r="U180" s="6">
+        <v>-0.3025775958680505</v>
+      </c>
+      <c r="V180" s="6">
+        <v>0.0056190615407104225</v>
+      </c>
+      <c r="W180" s="6">
+        <v>-0.063103834722019206</v>
+      </c>
+      <c r="X180" s="8">
+        <v>38.54523571428571</v>
+      </c>
+      <c r="Y180" s="6">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="Z180" s="6">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="AA180" s="8">
+        <v>5.1273138888888887</v>
+      </c>
+      <c r="AB180" s="8">
+        <v>16.245235714285716</v>
+      </c>
       <c r="AC180" s="8"/>
-      <c r="AD180" s="8"/>
-      <c r="AE180" s="6"/>
+      <c r="AD180" s="8">
+        <v>30.50714285714286</v>
+      </c>
+      <c r="AE180" s="6">
+        <v>0.35714285714285715</v>
+      </c>
       <c r="AF180" s="9"/>
-      <c r="AG180" s="5"/>
+      <c r="AG180" s="5">
+        <v>0</v>
+      </c>
       <c r="AH180" s="10">
         <v>2</v>
       </c>
@@ -23066,7 +23945,7 @@
         <v>19910</v>
       </c>
       <c r="B181" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C181" s="4">
         <v>44</v>
@@ -23102,25 +23981,59 @@
       <c t="s" r="N181" s="4">
         <v>52</v>
       </c>
-      <c r="O181" s="5"/>
-      <c r="P181" s="5"/>
-      <c r="Q181" s="6"/>
-      <c r="R181" s="7"/>
-      <c r="S181" s="6"/>
-      <c r="T181" s="6"/>
-      <c r="U181" s="6"/>
-      <c r="V181" s="6"/>
-      <c r="W181" s="6"/>
-      <c r="X181" s="8"/>
-      <c r="Y181" s="6"/>
-      <c r="Z181" s="6"/>
-      <c r="AA181" s="8"/>
-      <c r="AB181" s="8"/>
+      <c r="O181" s="5">
+        <v>4732.8999999999996</v>
+      </c>
+      <c r="P181" s="5">
+        <v>4732.8999999999996</v>
+      </c>
+      <c r="Q181" s="6">
+        <v>0.45158717988038632</v>
+      </c>
+      <c r="R181" s="7">
+        <v>44</v>
+      </c>
+      <c r="S181" s="6">
+        <v>0.15789473684210531</v>
+      </c>
+      <c r="T181" s="6">
+        <v>0.71872978512117314</v>
+      </c>
+      <c r="U181" s="6">
+        <v>0.43237258340552304</v>
+      </c>
+      <c r="V181" s="6">
+        <v>0.051619725749540456</v>
+      </c>
+      <c r="W181" s="6">
+        <v>0.025386338185890259</v>
+      </c>
+      <c r="X181" s="8">
+        <v>16.808331818181816</v>
+      </c>
+      <c r="Y181" s="6">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Z181" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA181" s="8">
+        <v>4.2544444444444443</v>
+      </c>
+      <c r="AB181" s="8">
+        <v>0.92888666666666664</v>
+      </c>
       <c r="AC181" s="8"/>
-      <c r="AD181" s="8"/>
-      <c r="AE181" s="6"/>
+      <c r="AD181" s="8">
+        <v>12.111363636363636</v>
+      </c>
+      <c r="AE181" s="6">
+        <v>1</v>
+      </c>
       <c r="AF181" s="9"/>
-      <c r="AG181" s="5"/>
+      <c r="AG181" s="5">
+        <v>0</v>
+      </c>
       <c r="AH181" s="10">
         <v>3</v>
       </c>
@@ -23239,7 +24152,9 @@
       <c r="AB182" s="8">
         <v>4.8523816326530609</v>
       </c>
-      <c r="AC182" s="8"/>
+      <c r="AC182" s="8">
+        <v>10.293036000000001</v>
+      </c>
       <c r="AD182" s="8">
         <v>16.089898484848483</v>
       </c>
@@ -23368,7 +24283,9 @@
       <c r="AB183" s="8">
         <v>2.5810613636363637</v>
       </c>
-      <c r="AC183" s="8"/>
+      <c r="AC183" s="8">
+        <v>7.9019810000000001</v>
+      </c>
       <c r="AD183" s="8">
         <v>15.449291489361704</v>
       </c>
@@ -23497,7 +24414,9 @@
       <c r="AB184" s="8">
         <v>6.0394736842105265</v>
       </c>
-      <c r="AC184" s="8"/>
+      <c r="AC184" s="8">
+        <v>11.237833</v>
+      </c>
       <c r="AD184" s="8">
         <v>19.814721666666667</v>
       </c>
@@ -23719,7 +24638,9 @@
       <c r="AB186" s="8">
         <v>5.0226214285714281</v>
       </c>
-      <c r="AC186" s="8"/>
+      <c r="AC186" s="8">
+        <v>11.477062999999999</v>
+      </c>
       <c r="AD186" s="8">
         <v>17.914446666666667</v>
       </c>
@@ -23770,7 +24691,7 @@
         <v>19927</v>
       </c>
       <c r="B187" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C187" s="4">
         <v>44</v>
@@ -23806,25 +24727,59 @@
       <c t="s" r="N187" s="4">
         <v>52</v>
       </c>
-      <c r="O187" s="5"/>
-      <c r="P187" s="5"/>
-      <c r="Q187" s="6"/>
-      <c r="R187" s="7"/>
-      <c r="S187" s="6"/>
-      <c r="T187" s="6"/>
-      <c r="U187" s="6"/>
-      <c r="V187" s="6"/>
-      <c r="W187" s="6"/>
-      <c r="X187" s="8"/>
-      <c r="Y187" s="6"/>
-      <c r="Z187" s="6"/>
-      <c r="AA187" s="8"/>
-      <c r="AB187" s="8"/>
+      <c r="O187" s="5">
+        <v>2249.0999999999999</v>
+      </c>
+      <c r="P187" s="5">
+        <v>2249.0999999999999</v>
+      </c>
+      <c r="Q187" s="6">
+        <v>-0.35924719878977462</v>
+      </c>
+      <c r="R187" s="7">
+        <v>30</v>
+      </c>
+      <c r="S187" s="6">
+        <v>-0.23076923076923073</v>
+      </c>
+      <c r="T187" s="6">
+        <v>0</v>
+      </c>
+      <c r="U187" s="6">
+        <v>-0.32072384509359303</v>
+      </c>
+      <c r="V187" s="6">
+        <v>0.096903428037881822</v>
+      </c>
+      <c r="W187" s="6">
+        <v>0.045994175447956961</v>
+      </c>
+      <c r="X187" s="8">
+        <v>32.743332000000002</v>
+      </c>
+      <c r="Y187" s="6">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="Z187" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA187" s="8">
+        <v>8.5166666666666675</v>
+      </c>
+      <c r="AB187" s="8">
+        <v>8.7763875000000002</v>
+      </c>
       <c r="AC187" s="8"/>
-      <c r="AD187" s="8"/>
-      <c r="AE187" s="6"/>
+      <c r="AD187" s="8">
+        <v>22.877332000000003</v>
+      </c>
+      <c r="AE187" s="6">
+        <v>0.40000000000000002</v>
+      </c>
       <c r="AF187" s="9"/>
-      <c r="AG187" s="5"/>
+      <c r="AG187" s="5">
+        <v>-189.69999999999999</v>
+      </c>
       <c r="AH187" s="10">
         <v>1</v>
       </c>
@@ -23945,7 +24900,9 @@
       <c r="AB188" s="8">
         <v>7.2378301587301586</v>
       </c>
-      <c r="AC188" s="8"/>
+      <c r="AC188" s="8">
+        <v>13.456348</v>
+      </c>
       <c r="AD188" s="8">
         <v>20.416401587301589</v>
       </c>
@@ -23996,7 +24953,7 @@
         <v>19930</v>
       </c>
       <c r="B189" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C189" s="4">
         <v>44</v>
@@ -24032,25 +24989,59 @@
       <c t="s" r="N189" s="4">
         <v>52</v>
       </c>
-      <c r="O189" s="5"/>
-      <c r="P189" s="5"/>
-      <c r="Q189" s="6"/>
-      <c r="R189" s="7"/>
-      <c r="S189" s="6"/>
-      <c r="T189" s="6"/>
-      <c r="U189" s="6"/>
-      <c r="V189" s="6"/>
-      <c r="W189" s="6"/>
-      <c r="X189" s="8"/>
-      <c r="Y189" s="6"/>
-      <c r="Z189" s="6"/>
-      <c r="AA189" s="8"/>
-      <c r="AB189" s="8"/>
+      <c r="O189" s="5">
+        <v>6583.6099999999997</v>
+      </c>
+      <c r="P189" s="5">
+        <v>6583.6099999999997</v>
+      </c>
+      <c r="Q189" s="6">
+        <v>0.28260471459185665</v>
+      </c>
+      <c r="R189" s="7">
+        <v>81</v>
+      </c>
+      <c r="S189" s="6">
+        <v>0.080000000000000071</v>
+      </c>
+      <c r="T189" s="6">
+        <v>0.27872928378199807</v>
+      </c>
+      <c r="U189" s="6">
+        <v>-0.015941876873022554</v>
+      </c>
+      <c r="V189" s="6">
+        <v>0.067225579887022477</v>
+      </c>
+      <c r="W189" s="6">
+        <v>0.041248950044124731</v>
+      </c>
+      <c r="X189" s="8">
+        <v>41.482618571428574</v>
+      </c>
+      <c r="Y189" s="6">
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="Z189" s="6">
+        <v>0.51428571428571423</v>
+      </c>
+      <c r="AA189" s="8">
+        <v>5.5866259259259259</v>
+      </c>
+      <c r="AB189" s="8">
+        <v>28.181355932203392</v>
+      </c>
       <c r="AC189" s="8"/>
-      <c r="AD189" s="8"/>
-      <c r="AE189" s="6"/>
+      <c r="AD189" s="8">
+        <v>35.461904285714283</v>
+      </c>
+      <c r="AE189" s="6">
+        <v>0.31428571428571428</v>
+      </c>
       <c r="AF189" s="9"/>
-      <c r="AG189" s="5"/>
+      <c r="AG189" s="5">
+        <v>0</v>
+      </c>
       <c r="AH189" s="10">
         <v>3</v>
       </c>
@@ -24091,7 +25082,7 @@
         <v>19931</v>
       </c>
       <c r="B190" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C190" s="4">
         <v>44</v>
@@ -24127,25 +25118,59 @@
       <c t="s" r="N190" s="4">
         <v>52</v>
       </c>
-      <c r="O190" s="5"/>
-      <c r="P190" s="5"/>
-      <c r="Q190" s="6"/>
-      <c r="R190" s="7"/>
-      <c r="S190" s="6"/>
-      <c r="T190" s="6"/>
-      <c r="U190" s="6"/>
-      <c r="V190" s="6"/>
-      <c r="W190" s="6"/>
-      <c r="X190" s="8"/>
-      <c r="Y190" s="6"/>
-      <c r="Z190" s="6"/>
-      <c r="AA190" s="8"/>
-      <c r="AB190" s="8"/>
+      <c r="O190" s="5">
+        <v>4997.8900000000003</v>
+      </c>
+      <c r="P190" s="5">
+        <v>4997.8900000000003</v>
+      </c>
+      <c r="Q190" s="6">
+        <v>-0.30676233686432741</v>
+      </c>
+      <c r="R190" s="7">
+        <v>65</v>
+      </c>
+      <c r="S190" s="6">
+        <v>-0.27777777777777779</v>
+      </c>
+      <c r="T190" s="6">
+        <v>0.33560702616504162</v>
+      </c>
+      <c r="U190" s="6">
+        <v>0.014467505287231211</v>
+      </c>
+      <c r="V190" s="6">
+        <v>0.088377995514106952</v>
+      </c>
+      <c r="W190" s="6">
+        <v>0.060672303712166531</v>
+      </c>
+      <c r="X190" s="8">
+        <v>23.538</v>
+      </c>
+      <c r="Y190" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z190" s="6">
+        <v>0.040000000000000001</v>
+      </c>
+      <c r="AA190" s="8">
+        <v>3.6816934426229508</v>
+      </c>
+      <c r="AB190" s="8">
+        <v>5.8902791666666667</v>
+      </c>
       <c r="AC190" s="8"/>
-      <c r="AD190" s="8"/>
-      <c r="AE190" s="6"/>
+      <c r="AD190" s="8">
+        <v>16.611332000000001</v>
+      </c>
+      <c r="AE190" s="6">
+        <v>0.92000000000000004</v>
+      </c>
       <c r="AF190" s="9"/>
-      <c r="AG190" s="5"/>
+      <c r="AG190" s="5">
+        <v>-234</v>
+      </c>
       <c r="AH190" s="10">
         <v>2</v>
       </c>
@@ -24264,7 +25289,9 @@
       <c r="AB191" s="8">
         <v>5.2326395833333335</v>
       </c>
-      <c r="AC191" s="8"/>
+      <c r="AC191" s="8">
+        <v>10.356787000000001</v>
+      </c>
       <c r="AD191" s="8">
         <v>17.261110416666668</v>
       </c>
@@ -24391,7 +25418,9 @@
       <c r="AB192" s="8">
         <v>13.315027868852457</v>
       </c>
-      <c r="AC192" s="8"/>
+      <c r="AC192" s="8">
+        <v>16.021311000000001</v>
+      </c>
       <c r="AD192" s="8">
         <v>22.967486885245901</v>
       </c>
@@ -24518,7 +25547,9 @@
       <c r="AB193" s="8">
         <v>8.954699999999999</v>
       </c>
-      <c r="AC193" s="8"/>
+      <c r="AC193" s="8">
+        <v>15.986903</v>
+      </c>
       <c r="AD193" s="8">
         <v>21.121970454545455</v>
       </c>
@@ -24649,7 +25680,9 @@
       <c r="AB194" s="8">
         <v>19.703125</v>
       </c>
-      <c r="AC194" s="8"/>
+      <c r="AC194" s="8">
+        <v>25.457568999999999</v>
+      </c>
       <c r="AD194" s="8">
         <v>32.033331250000003</v>
       </c>
@@ -24778,7 +25811,9 @@
       <c r="AB195" s="8">
         <v>6.2598044117647058</v>
       </c>
-      <c r="AC195" s="8"/>
+      <c r="AC195" s="8">
+        <v>10.736027999999999</v>
+      </c>
       <c r="AD195" s="8">
         <v>17.668136764705881</v>
       </c>
@@ -24907,7 +25942,9 @@
       <c r="AB196" s="8">
         <v>60.310000000000002</v>
       </c>
-      <c r="AC196" s="8"/>
+      <c r="AC196" s="8">
+        <v>70.143332999999998</v>
+      </c>
       <c r="AD196" s="8">
         <v>66.411108333333331</v>
       </c>
@@ -25036,7 +26073,9 @@
       <c r="AB197" s="8">
         <v>5.133582089552239</v>
       </c>
-      <c r="AC197" s="8"/>
+      <c r="AC197" s="8">
+        <v>7.6666730000000003</v>
+      </c>
       <c r="AD197" s="8">
         <v>14.243720289855071</v>
       </c>
@@ -25165,7 +26204,9 @@
       <c r="AB198" s="8">
         <v>8.370000000000001</v>
       </c>
-      <c r="AC198" s="8"/>
+      <c r="AC198" s="8">
+        <v>17.013332999999999</v>
+      </c>
       <c r="AD198" s="8">
         <v>23.93</v>
       </c>
@@ -25216,7 +26257,7 @@
         <v>19951</v>
       </c>
       <c r="B199" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C199" s="4">
         <v>44</v>
@@ -25252,25 +26293,59 @@
       <c t="s" r="N199" s="4">
         <v>52</v>
       </c>
-      <c r="O199" s="5"/>
-      <c r="P199" s="5"/>
-      <c r="Q199" s="6"/>
-      <c r="R199" s="7"/>
-      <c r="S199" s="6"/>
-      <c r="T199" s="6"/>
-      <c r="U199" s="6"/>
-      <c r="V199" s="6"/>
-      <c r="W199" s="6"/>
-      <c r="X199" s="8"/>
-      <c r="Y199" s="6"/>
-      <c r="Z199" s="6"/>
-      <c r="AA199" s="8"/>
-      <c r="AB199" s="8"/>
+      <c r="O199" s="5">
+        <v>5729.2600000000002</v>
+      </c>
+      <c r="P199" s="5">
+        <v>5729.2600000000002</v>
+      </c>
+      <c r="Q199" s="6">
+        <v>-0.3073191845380443</v>
+      </c>
+      <c r="R199" s="7">
+        <v>56</v>
+      </c>
+      <c r="S199" s="6">
+        <v>-0.3707865168539326</v>
+      </c>
+      <c r="T199" s="6">
+        <v>0.93963147073094955</v>
+      </c>
+      <c r="U199" s="6">
+        <v>0.58058859259310969</v>
+      </c>
+      <c r="V199" s="6">
+        <v>0.015428955921008996</v>
+      </c>
+      <c r="W199" s="6">
+        <v>-0.0060397852427713167</v>
+      </c>
+      <c r="X199" s="8">
+        <v>19.982577272727273</v>
+      </c>
+      <c r="Y199" s="6">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z199" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA199" s="8">
+        <v>5.2380946428571429</v>
+      </c>
+      <c r="AB199" s="8">
+        <v>1.8977272727272727</v>
+      </c>
       <c r="AC199" s="8"/>
-      <c r="AD199" s="8"/>
-      <c r="AE199" s="6"/>
+      <c r="AD199" s="8">
+        <v>13.963636363636363</v>
+      </c>
+      <c r="AE199" s="6">
+        <v>0.90909090909090906</v>
+      </c>
       <c r="AF199" s="9"/>
-      <c r="AG199" s="5"/>
+      <c r="AG199" s="5">
+        <v>-242.59999999999999</v>
+      </c>
       <c r="AH199" s="10">
         <v>1</v>
       </c>
@@ -25311,7 +26386,7 @@
         <v>19954</v>
       </c>
       <c r="B200" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C200" s="4">
         <v>44</v>
@@ -25347,25 +26422,59 @@
       <c t="s" r="N200" s="4">
         <v>52</v>
       </c>
-      <c r="O200" s="5"/>
-      <c r="P200" s="5"/>
-      <c r="Q200" s="6"/>
-      <c r="R200" s="7"/>
-      <c r="S200" s="6"/>
-      <c r="T200" s="6"/>
-      <c r="U200" s="6"/>
-      <c r="V200" s="6"/>
-      <c r="W200" s="6"/>
-      <c r="X200" s="8"/>
-      <c r="Y200" s="6"/>
-      <c r="Z200" s="6"/>
-      <c r="AA200" s="8"/>
-      <c r="AB200" s="8"/>
+      <c r="O200" s="5">
+        <v>2438.48</v>
+      </c>
+      <c r="P200" s="5">
+        <v>2438.48</v>
+      </c>
+      <c r="Q200" s="6">
+        <v>0.40120785855068464</v>
+      </c>
+      <c r="R200" s="7">
+        <v>25</v>
+      </c>
+      <c r="S200" s="6">
+        <v>-0.038461538461538436</v>
+      </c>
+      <c r="T200" s="6">
+        <v>0</v>
+      </c>
+      <c r="U200" s="6">
+        <v>-0.37323660641055084</v>
+      </c>
+      <c r="V200" s="6">
+        <v>0.090445482431678742</v>
+      </c>
+      <c r="W200" s="6">
+        <v>0.040648067648699188</v>
+      </c>
+      <c r="X200" s="8">
+        <v>32.538891666666665</v>
+      </c>
+      <c r="Y200" s="6">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z200" s="6">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="AA200" s="8">
+        <v>16.733332000000001</v>
+      </c>
+      <c r="AB200" s="8">
+        <v>3</v>
+      </c>
       <c r="AC200" s="8"/>
-      <c r="AD200" s="8"/>
-      <c r="AE200" s="6"/>
+      <c r="AD200" s="8">
+        <v>24.211108333333332</v>
+      </c>
+      <c r="AE200" s="6">
+        <v>0.33333333333333331</v>
+      </c>
       <c r="AF200" s="9"/>
-      <c r="AG200" s="5"/>
+      <c r="AG200" s="5">
+        <v>-190</v>
+      </c>
       <c r="AH200" s="10">
         <v>3</v>
       </c>
@@ -25577,7 +26686,9 @@
       <c r="AB202" s="8">
         <v>7.2992739130434776</v>
       </c>
-      <c r="AC202" s="8"/>
+      <c r="AC202" s="8">
+        <v>12.832608</v>
+      </c>
       <c r="AD202" s="8">
         <v>18.828668</v>
       </c>
@@ -25799,7 +26910,9 @@
       <c r="AB204" s="8">
         <v>11.612364516129032</v>
       </c>
-      <c r="AC204" s="8"/>
+      <c r="AC204" s="8">
+        <v>20.233577</v>
+      </c>
       <c r="AD204" s="8">
         <v>26.398959375</v>
       </c>
@@ -25850,7 +26963,7 @@
         <v>19959</v>
       </c>
       <c r="B205" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C205" s="4">
         <v>44</v>
@@ -25886,25 +26999,55 @@
       <c t="s" r="N205" s="4">
         <v>52</v>
       </c>
-      <c r="O205" s="5"/>
-      <c r="P205" s="5"/>
+      <c r="O205" s="5">
+        <v>3478.6799999999998</v>
+      </c>
+      <c r="P205" s="5">
+        <v>3478.6799999999998</v>
+      </c>
       <c r="Q205" s="6"/>
-      <c r="R205" s="7"/>
+      <c r="R205" s="7">
+        <v>45</v>
+      </c>
       <c r="S205" s="6"/>
-      <c r="T205" s="6"/>
-      <c r="U205" s="6"/>
-      <c r="V205" s="6"/>
-      <c r="W205" s="6"/>
-      <c r="X205" s="8"/>
-      <c r="Y205" s="6"/>
-      <c r="Z205" s="6"/>
-      <c r="AA205" s="8"/>
-      <c r="AB205" s="8"/>
+      <c r="T205" s="6">
+        <v>1.2638164188715262</v>
+      </c>
+      <c r="U205" s="6">
+        <v>0.88543726355974106</v>
+      </c>
+      <c r="V205" s="6">
+        <v>0.19436697252981017</v>
+      </c>
+      <c r="W205" s="6">
+        <v>0.13295574758241632</v>
+      </c>
+      <c r="X205" s="8">
+        <v>25.572220000000002</v>
+      </c>
+      <c r="Y205" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z205" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA205" s="8">
+        <v>5.3948155555555548</v>
+      </c>
+      <c r="AB205" s="8">
+        <v>3.3066666666666666</v>
+      </c>
       <c r="AC205" s="8"/>
-      <c r="AD205" s="8"/>
-      <c r="AE205" s="6"/>
+      <c r="AD205" s="8">
+        <v>15.224446666666667</v>
+      </c>
+      <c r="AE205" s="6">
+        <v>0.80000000000000004</v>
+      </c>
       <c r="AF205" s="9"/>
-      <c r="AG205" s="5"/>
+      <c r="AG205" s="5">
+        <v>-234.40000000000001</v>
+      </c>
       <c r="AH205" s="10">
         <v>3</v>
       </c>
@@ -25945,7 +27088,7 @@
         <v>19961</v>
       </c>
       <c r="B206" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C206" s="4">
         <v>44</v>
@@ -25981,25 +27124,55 @@
       <c t="s" r="N206" s="4">
         <v>52</v>
       </c>
-      <c r="O206" s="5"/>
-      <c r="P206" s="5"/>
+      <c r="O206" s="5">
+        <v>3750.5</v>
+      </c>
+      <c r="P206" s="5">
+        <v>3750.5</v>
+      </c>
       <c r="Q206" s="6"/>
-      <c r="R206" s="7"/>
+      <c r="R206" s="7">
+        <v>41</v>
+      </c>
       <c r="S206" s="6"/>
-      <c r="T206" s="6"/>
-      <c r="U206" s="6"/>
-      <c r="V206" s="6"/>
-      <c r="W206" s="6"/>
-      <c r="X206" s="8"/>
-      <c r="Y206" s="6"/>
-      <c r="Z206" s="6"/>
-      <c r="AA206" s="8"/>
-      <c r="AB206" s="8"/>
+      <c r="T206" s="6">
+        <v>0.36051926409812024</v>
+      </c>
+      <c r="U206" s="6">
+        <v>-0.0059732035728569527</v>
+      </c>
+      <c r="V206" s="6">
+        <v>0.036785895213971471</v>
+      </c>
+      <c r="W206" s="6">
+        <v>0.020668044260765232</v>
+      </c>
+      <c r="X206" s="8">
+        <v>34.956347619047619</v>
+      </c>
+      <c r="Y206" s="6">
+        <v>0.52380952380952384</v>
+      </c>
+      <c r="Z206" s="6">
+        <v>0.23809523809523808</v>
+      </c>
+      <c r="AA206" s="8">
+        <v>10.616667441860466</v>
+      </c>
+      <c r="AB206" s="8">
+        <v>7.6212944444444446</v>
+      </c>
       <c r="AC206" s="8"/>
-      <c r="AD206" s="8"/>
-      <c r="AE206" s="6"/>
+      <c r="AD206" s="8">
+        <v>23.307938095238097</v>
+      </c>
+      <c r="AE206" s="6">
+        <v>0.42857142857142855</v>
+      </c>
       <c r="AF206" s="9"/>
-      <c r="AG206" s="5"/>
+      <c r="AG206" s="5">
+        <v>-338.19999999999999</v>
+      </c>
       <c r="AH206" s="10">
         <v>2</v>
       </c>
@@ -26209,7 +27382,9 @@
       <c r="AB208" s="8">
         <v>7.4807978260869561</v>
       </c>
-      <c r="AC208" s="8"/>
+      <c r="AC208" s="8">
+        <v>18.737179000000001</v>
+      </c>
       <c r="AD208" s="8">
         <v>25.815580434782607</v>
       </c>
@@ -26518,7 +27693,9 @@
       <c r="AB211" s="8">
         <v>13.463492063492064</v>
       </c>
-      <c r="AC211" s="8"/>
+      <c r="AC211" s="8">
+        <v>22.783332999999999</v>
+      </c>
       <c r="AD211" s="8">
         <v>29.70132222222222</v>
       </c>
@@ -26993,22 +28170,24 @@
       <c t="s" r="AB216" s="14">
         <v>315</v>
       </c>
-      <c r="AC216" s="14"/>
+      <c t="s" r="AC216" s="14">
+        <v>316</v>
+      </c>
       <c t="s" r="AD216" s="14">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="AE216" s="14">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="AF216" s="14"/>
       <c t="s" r="AG216" s="14">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c t="s" r="AH216" s="14">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="AI216" s="14">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="AJ216" s="15"/>
       <c t="s" r="AK216" s="15">
@@ -27018,10 +28197,10 @@
         <v>52</v>
       </c>
       <c t="s" r="AM216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c t="s" r="AN216" s="14">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="AO216" s="15"/>
       <c r="AP216" s="15"/>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -912,36 +912,36 @@
   </si>
   <si>
     <t>214
-167</t>
-  </si>
-  <si>
-    <t>36</t>
-  </si>
-  <si>
-    <t>R$ 1.581.523,87</t>
-  </si>
-  <si>
-    <t>R$ 8.884,97
-R$ 9.098,55</t>
-  </si>
-  <si>
-    <t>(4.4%)
-(2.1%)</t>
-  </si>
-  <si>
-    <t>94.3</t>
-  </si>
-  <si>
-    <t>(6.7%)</t>
-  </si>
-  <si>
-    <t>10.2%</t>
-  </si>
-  <si>
-    <t>(41.3%)</t>
-  </si>
-  <si>
-    <t>2.6%</t>
+168</t>
+  </si>
+  <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>R$ 1.596.490,56</t>
+  </si>
+  <si>
+    <t>R$ 8.869,39
+R$ 9.114,16</t>
+  </si>
+  <si>
+    <t>(4.7%)
+(2.0%)</t>
+  </si>
+  <si>
+    <t>94.2</t>
+  </si>
+  <si>
+    <t>(6.9%)</t>
+  </si>
+  <si>
+    <t>10.4%</t>
+  </si>
+  <si>
+    <t>(40.9%)</t>
+  </si>
+  <si>
+    <t>2.7%</t>
   </si>
   <si>
     <t>0.5%</t>
@@ -950,7 +950,7 @@
     <t>32.3</t>
   </si>
   <si>
-    <t>57.8%</t>
+    <t>57.7%</t>
   </si>
   <si>
     <t>17.6%</t>
@@ -962,16 +962,16 @@
     <t>10.3</t>
   </si>
   <si>
-    <t>16.6</t>
-  </si>
-  <si>
-    <t>22.9</t>
-  </si>
-  <si>
-    <t>62.3%</t>
-  </si>
-  <si>
-    <t>-R$ 35.271,90</t>
+    <t>17.2</t>
+  </si>
+  <si>
+    <t>23.0</t>
+  </si>
+  <si>
+    <t>62.1%</t>
+  </si>
+  <si>
+    <t>-R$ 38.516,61</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2894,7 +2894,9 @@
       <c r="AB12" s="8">
         <v>7.0117796992481205</v>
       </c>
-      <c r="AC12" s="8"/>
+      <c r="AC12" s="8">
+        <v>11.690367</v>
+      </c>
       <c r="AD12" s="8">
         <v>18.107005072463767</v>
       </c>
@@ -4821,7 +4823,9 @@
       <c r="AB27" s="8">
         <v>7.037179487179487</v>
       </c>
-      <c r="AC27" s="8"/>
+      <c r="AC27" s="8">
+        <v>12.752625999999999</v>
+      </c>
       <c r="AD27" s="8">
         <v>20.712392307692308</v>
       </c>
@@ -6319,7 +6323,9 @@
       <c r="AB39" s="8">
         <v>5.9204081632653063</v>
       </c>
-      <c r="AC39" s="8"/>
+      <c r="AC39" s="8">
+        <v>8.7445149999999998</v>
+      </c>
       <c r="AD39" s="8">
         <v>15.408630357142856</v>
       </c>
@@ -6632,7 +6638,7 @@
         <v>19579</v>
       </c>
       <c r="B42" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C42" s="4">
         <v>44</v>
@@ -6668,25 +6674,59 @@
       <c t="s" r="N42" s="4">
         <v>52</v>
       </c>
-      <c r="O42" s="5"/>
-      <c r="P42" s="5"/>
-      <c r="Q42" s="6"/>
-      <c r="R42" s="7"/>
-      <c r="S42" s="6"/>
-      <c r="T42" s="6"/>
-      <c r="U42" s="6"/>
-      <c r="V42" s="6"/>
-      <c r="W42" s="6"/>
-      <c r="X42" s="8"/>
-      <c r="Y42" s="6"/>
-      <c r="Z42" s="6"/>
-      <c r="AA42" s="8"/>
-      <c r="AB42" s="8"/>
+      <c r="O42" s="5">
+        <v>11721.98</v>
+      </c>
+      <c r="P42" s="5">
+        <v>11721.98</v>
+      </c>
+      <c r="Q42" s="6">
+        <v>0.07740173127227723</v>
+      </c>
+      <c r="R42" s="7">
+        <v>132</v>
+      </c>
+      <c r="S42" s="6">
+        <v>0.24528301886792447</v>
+      </c>
+      <c r="T42" s="6">
+        <v>0.30433066768583467</v>
+      </c>
+      <c r="U42" s="6">
+        <v>0.0028926853654416746</v>
+      </c>
+      <c r="V42" s="6">
+        <v>0.032554739045792605</v>
+      </c>
+      <c r="W42" s="6">
+        <v>0.0088198410166200596</v>
+      </c>
+      <c r="X42" s="8">
+        <v>34.740369999999999</v>
+      </c>
+      <c r="Y42" s="6">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="Z42" s="6">
+        <v>0.24444444444444444</v>
+      </c>
+      <c r="AA42" s="8">
+        <v>7.6997418604651164</v>
+      </c>
+      <c r="AB42" s="8">
+        <v>11.746255056179775</v>
+      </c>
       <c r="AC42" s="8"/>
-      <c r="AD42" s="8"/>
-      <c r="AE42" s="6"/>
+      <c r="AD42" s="8">
+        <v>27.200925555555553</v>
+      </c>
+      <c r="AE42" s="6">
+        <v>0.35555555555555557</v>
+      </c>
       <c r="AF42" s="9"/>
-      <c r="AG42" s="5"/>
+      <c r="AG42" s="5">
+        <v>0</v>
+      </c>
       <c r="AH42" s="10">
         <v>3</v>
       </c>
@@ -6805,7 +6845,9 @@
       <c r="AB43" s="8">
         <v>9.3499999999999996</v>
       </c>
-      <c r="AC43" s="8"/>
+      <c r="AC43" s="8">
+        <v>22.305713999999998</v>
+      </c>
       <c r="AD43" s="8">
         <v>28.964734782608698</v>
       </c>
@@ -7194,7 +7236,9 @@
       <c r="AB46" s="8">
         <v>8.3869042857142855</v>
       </c>
-      <c r="AC46" s="8"/>
+      <c r="AC46" s="8">
+        <v>11.856904</v>
+      </c>
       <c r="AD46" s="8">
         <v>18.806189999999997</v>
       </c>
@@ -7712,7 +7756,9 @@
       <c r="AB50" s="8">
         <v>3.1123340000000002</v>
       </c>
-      <c r="AC50" s="8"/>
+      <c r="AC50" s="8">
+        <v>5.9328450000000004</v>
+      </c>
       <c r="AD50" s="8">
         <v>13.683333333333334</v>
       </c>
@@ -8327,7 +8373,9 @@
       <c r="AB55" s="8">
         <v>38.469230769230769</v>
       </c>
-      <c r="AC55" s="8"/>
+      <c r="AC55" s="8">
+        <v>42.301934000000003</v>
+      </c>
       <c r="AD55" s="8">
         <v>49.247115384615384</v>
       </c>
@@ -9200,7 +9248,9 @@
       <c r="AB62" s="8">
         <v>4.8700000000000001</v>
       </c>
-      <c r="AC62" s="8"/>
+      <c r="AC62" s="8">
+        <v>8.2641349999999996</v>
+      </c>
       <c r="AD62" s="8">
         <v>14.80673076923077</v>
       </c>
@@ -10327,7 +10377,9 @@
       <c r="AB71" s="8">
         <v>5.1432092592592591</v>
       </c>
-      <c r="AC71" s="8"/>
+      <c r="AC71" s="8">
+        <v>9.2964819999999992</v>
+      </c>
       <c r="AD71" s="8">
         <v>17.166059999999998</v>
       </c>
@@ -10805,7 +10857,9 @@
       <c r="AB75" s="8">
         <v>4.6576374999999999</v>
       </c>
-      <c r="AC75" s="8"/>
+      <c r="AC75" s="8">
+        <v>9.1980219999999999</v>
+      </c>
       <c r="AD75" s="8">
         <v>15.743332000000001</v>
       </c>
@@ -12160,7 +12214,9 @@
       <c r="AB86" s="8">
         <v>7.2873134328358207</v>
       </c>
-      <c r="AC86" s="8"/>
+      <c r="AC86" s="8">
+        <v>20.650645999999998</v>
+      </c>
       <c r="AD86" s="8">
         <v>28.789613043478262</v>
       </c>
@@ -12642,7 +12698,9 @@
       <c r="AB90" s="8">
         <v>15.317628846153847</v>
       </c>
-      <c r="AC90" s="8"/>
+      <c r="AC90" s="8">
+        <v>23.167020999999998</v>
+      </c>
       <c r="AD90" s="8">
         <v>29.30462962962963</v>
       </c>
@@ -15007,7 +15065,9 @@
       <c r="AB109" s="8">
         <v>8.2580448275862075</v>
       </c>
-      <c r="AC109" s="8"/>
+      <c r="AC109" s="8">
+        <v>13.598849</v>
+      </c>
       <c r="AD109" s="8">
         <v>21.538506896551727</v>
       </c>
@@ -17108,7 +17168,9 @@
       <c r="AB126" s="8">
         <v>19.246109999999998</v>
       </c>
-      <c r="AC126" s="8"/>
+      <c r="AC126" s="8">
+        <v>26.546111</v>
+      </c>
       <c r="AD126" s="8">
         <v>32.736022580645162</v>
       </c>
@@ -20039,7 +20101,9 @@
       <c r="AB149" s="8">
         <v>62.44140927835052</v>
       </c>
-      <c r="AC149" s="8"/>
+      <c r="AC149" s="8">
+        <v>89.216063000000005</v>
+      </c>
       <c r="AD149" s="8">
         <v>77.362451724137927</v>
       </c>
@@ -20641,7 +20705,7 @@
         <v>0.01616377389433904</v>
       </c>
       <c r="W154" s="6">
-        <v>-0.0063074518845109423</v>
+        <v>-0.0043540135359165259</v>
       </c>
       <c r="X154" s="8">
         <v>31.649548648648651</v>
@@ -21588,7 +21652,9 @@
       <c r="AB162" s="8">
         <v>3.5963531249999998</v>
       </c>
-      <c r="AC162" s="8"/>
+      <c r="AC162" s="8">
+        <v>13.533727000000001</v>
+      </c>
       <c r="AD162" s="8">
         <v>21.324242424242424</v>
       </c>
@@ -23253,7 +23319,9 @@
       <c r="AB175" s="8">
         <v>3.0247484848484847</v>
       </c>
-      <c r="AC175" s="8"/>
+      <c r="AC175" s="8">
+        <v>11.366650999999999</v>
+      </c>
       <c r="AD175" s="8">
         <v>18.05095142857143</v>
       </c>
@@ -23376,7 +23444,9 @@
       <c r="AB176" s="8">
         <v>7.8260437500000002</v>
       </c>
-      <c r="AC176" s="8"/>
+      <c r="AC176" s="8">
+        <v>10.864582</v>
+      </c>
       <c r="AD176" s="8">
         <v>17.819793749999999</v>
       </c>
@@ -23894,7 +23964,9 @@
       <c r="AB180" s="8">
         <v>16.245235714285716</v>
       </c>
-      <c r="AC180" s="8"/>
+      <c r="AC180" s="8">
+        <v>22.572617999999999</v>
+      </c>
       <c r="AD180" s="8">
         <v>30.50714285714286</v>
       </c>
@@ -24023,7 +24095,9 @@
       <c r="AB181" s="8">
         <v>0.92888666666666664</v>
       </c>
-      <c r="AC181" s="8"/>
+      <c r="AC181" s="8">
+        <v>4.9042500000000002</v>
+      </c>
       <c r="AD181" s="8">
         <v>12.111363636363636</v>
       </c>
@@ -24769,7 +24843,9 @@
       <c r="AB187" s="8">
         <v>8.7763875000000002</v>
       </c>
-      <c r="AC187" s="8"/>
+      <c r="AC187" s="8">
+        <v>16.478387999999999</v>
+      </c>
       <c r="AD187" s="8">
         <v>22.877332000000003</v>
       </c>
@@ -25031,7 +25107,9 @@
       <c r="AB189" s="8">
         <v>28.181355932203392</v>
       </c>
-      <c r="AC189" s="8"/>
+      <c r="AC189" s="8">
+        <v>33.726894000000001</v>
+      </c>
       <c r="AD189" s="8">
         <v>35.461904285714283</v>
       </c>
@@ -25160,7 +25238,9 @@
       <c r="AB190" s="8">
         <v>5.8902791666666667</v>
       </c>
-      <c r="AC190" s="8"/>
+      <c r="AC190" s="8">
+        <v>9.9542769999999994</v>
+      </c>
       <c r="AD190" s="8">
         <v>16.611332000000001</v>
       </c>
@@ -26335,7 +26415,9 @@
       <c r="AB199" s="8">
         <v>1.8977272727272727</v>
       </c>
-      <c r="AC199" s="8"/>
+      <c r="AC199" s="8">
+        <v>7.0068169999999999</v>
+      </c>
       <c r="AD199" s="8">
         <v>13.963636363636363</v>
       </c>
@@ -26464,7 +26546,9 @@
       <c r="AB200" s="8">
         <v>3</v>
       </c>
-      <c r="AC200" s="8"/>
+      <c r="AC200" s="8">
+        <v>17.252776999999998</v>
+      </c>
       <c r="AD200" s="8">
         <v>24.211108333333332</v>
       </c>
@@ -27037,7 +27121,9 @@
       <c r="AB205" s="8">
         <v>3.3066666666666666</v>
       </c>
-      <c r="AC205" s="8"/>
+      <c r="AC205" s="8">
+        <v>8.3243740000000006</v>
+      </c>
       <c r="AD205" s="8">
         <v>15.224446666666667</v>
       </c>
@@ -27162,7 +27248,9 @@
       <c r="AB206" s="8">
         <v>7.6212944444444446</v>
       </c>
-      <c r="AC206" s="8"/>
+      <c r="AC206" s="8">
+        <v>18.43872</v>
+      </c>
       <c r="AD206" s="8">
         <v>23.307938095238097</v>
       </c>
@@ -27213,7 +27301,7 @@
         <v>19962</v>
       </c>
       <c r="B207" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C207" s="4">
         <v>44</v>
@@ -27249,25 +27337,55 @@
       <c t="s" r="N207" s="4">
         <v>52</v>
       </c>
-      <c r="O207" s="5"/>
-      <c r="P207" s="5"/>
+      <c r="O207" s="5">
+        <v>3244.71</v>
+      </c>
+      <c r="P207" s="5">
+        <v>3244.71</v>
+      </c>
       <c r="Q207" s="6"/>
-      <c r="R207" s="7"/>
+      <c r="R207" s="7">
+        <v>36</v>
+      </c>
       <c r="S207" s="6"/>
-      <c r="T207" s="6"/>
-      <c r="U207" s="6"/>
-      <c r="V207" s="6"/>
-      <c r="W207" s="6"/>
-      <c r="X207" s="8"/>
-      <c r="Y207" s="6"/>
-      <c r="Z207" s="6"/>
-      <c r="AA207" s="8"/>
-      <c r="AB207" s="8"/>
+      <c r="T207" s="6">
+        <v>0</v>
+      </c>
+      <c r="U207" s="6">
+        <v>-0.31235457097860825</v>
+      </c>
+      <c r="V207" s="6">
+        <v>0.03785345993940907</v>
+      </c>
+      <c r="W207" s="6">
+        <v>-0.0080427834845024672</v>
+      </c>
+      <c r="X207" s="8">
+        <v>27.603966666666668</v>
+      </c>
+      <c r="Y207" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z207" s="6">
+        <v>0.095238095238095233</v>
+      </c>
+      <c r="AA207" s="8">
+        <v>7.234285714285714</v>
+      </c>
+      <c r="AB207" s="8">
+        <v>7.3912714285714287</v>
+      </c>
       <c r="AC207" s="8"/>
-      <c r="AD207" s="8"/>
-      <c r="AE207" s="6"/>
+      <c r="AD207" s="8">
+        <v>20.996033333333333</v>
+      </c>
+      <c r="AE207" s="6">
+        <v>0.76190476190476186</v>
+      </c>
       <c r="AF207" s="9"/>
-      <c r="AG207" s="5"/>
+      <c r="AG207" s="5">
+        <v>-3244.71</v>
+      </c>
       <c r="AH207" s="10">
         <v>4</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -912,30 +912,30 @@
   </si>
   <si>
     <t>214
-168</t>
-  </si>
-  <si>
-    <t>34</t>
-  </si>
-  <si>
-    <t>R$ 1.596.490,56</t>
-  </si>
-  <si>
-    <t>R$ 8.869,39
-R$ 9.114,16</t>
+169</t>
+  </si>
+  <si>
+    <t>33</t>
+  </si>
+  <si>
+    <t>R$ 1.602.041,82</t>
+  </si>
+  <si>
+    <t>R$ 8.851,06
+R$ 9.093,08</t>
   </si>
   <si>
     <t>(4.7%)
-(2.0%)</t>
-  </si>
-  <si>
-    <t>94.2</t>
+(2.1%)</t>
+  </si>
+  <si>
+    <t>94.1</t>
   </si>
   <si>
     <t>(6.9%)</t>
   </si>
   <si>
-    <t>10.4%</t>
+    <t>10.3%</t>
   </si>
   <si>
     <t>(40.9%)</t>
@@ -950,19 +950,19 @@
     <t>32.3</t>
   </si>
   <si>
-    <t>57.7%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
+    <t>57.4%</t>
+  </si>
+  <si>
+    <t>17.7%</t>
   </si>
   <si>
     <t>6.3</t>
   </si>
   <si>
-    <t>10.3</t>
-  </si>
-  <si>
-    <t>17.2</t>
+    <t>10.4</t>
+  </si>
+  <si>
+    <t>17.3</t>
   </si>
   <si>
     <t>23.0</t>
@@ -6716,7 +6716,9 @@
       <c r="AB42" s="8">
         <v>11.746255056179775</v>
       </c>
-      <c r="AC42" s="8"/>
+      <c r="AC42" s="8">
+        <v>20.48292</v>
+      </c>
       <c r="AD42" s="8">
         <v>27.200925555555553</v>
       </c>
@@ -14148,7 +14150,7 @@
         <v>19719</v>
       </c>
       <c r="B102" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C102" s="4">
         <v>44</v>
@@ -14184,25 +14186,61 @@
       <c t="s" r="N102" s="4">
         <v>52</v>
       </c>
-      <c r="O102" s="5"/>
-      <c r="P102" s="5"/>
-      <c r="Q102" s="6"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="6"/>
-      <c r="T102" s="6"/>
-      <c r="U102" s="6"/>
-      <c r="V102" s="6"/>
-      <c r="W102" s="6"/>
-      <c r="X102" s="8"/>
-      <c r="Y102" s="6"/>
-      <c r="Z102" s="6"/>
-      <c r="AA102" s="8"/>
-      <c r="AB102" s="8"/>
-      <c r="AC102" s="8"/>
-      <c r="AD102" s="8"/>
-      <c r="AE102" s="6"/>
+      <c r="O102" s="5">
+        <v>5551.2600000000002</v>
+      </c>
+      <c r="P102" s="5">
+        <v>5551.2600000000002</v>
+      </c>
+      <c r="Q102" s="6">
+        <v>-0.24083256977968626</v>
+      </c>
+      <c r="R102" s="7">
+        <v>66</v>
+      </c>
+      <c r="S102" s="6">
+        <v>-0.22352941176470587</v>
+      </c>
+      <c r="T102" s="6">
+        <v>4.5449141276034631E-05</v>
+      </c>
+      <c r="U102" s="6">
+        <v>-0.31928205488483696</v>
+      </c>
+      <c r="V102" s="6">
+        <v>0.059481360988316169</v>
+      </c>
+      <c r="W102" s="6">
+        <v>0.040480269344256976</v>
+      </c>
+      <c r="X102" s="8">
+        <v>44.985506521739126</v>
+      </c>
+      <c r="Y102" s="6">
+        <v>0.065217391304347824</v>
+      </c>
+      <c r="Z102" s="6">
+        <v>0.41304347826086957</v>
+      </c>
+      <c r="AA102" s="8">
+        <v>7.2404411764705889</v>
+      </c>
+      <c r="AB102" s="8">
+        <v>21.6470825</v>
+      </c>
+      <c r="AC102" s="8">
+        <v>28.995346000000001</v>
+      </c>
+      <c r="AD102" s="8">
+        <v>32.503260869565217</v>
+      </c>
+      <c r="AE102" s="6">
+        <v>0.39130434782608697</v>
+      </c>
       <c r="AF102" s="9"/>
-      <c r="AG102" s="5"/>
+      <c r="AG102" s="5">
+        <v>0</v>
+      </c>
       <c r="AH102" s="10">
         <v>2</v>
       </c>
@@ -27375,7 +27413,9 @@
       <c r="AB207" s="8">
         <v>7.3912714285714287</v>
       </c>
-      <c r="AC207" s="8"/>
+      <c r="AC207" s="8">
+        <v>14.162481</v>
+      </c>
       <c r="AD207" s="8">
         <v>20.996033333333333</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -911,34 +911,37 @@
     <t>GUIMARAES FRAGA,MARESSA</t>
   </si>
   <si>
-    <t>214
-169</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>R$ 1.602.041,82</t>
-  </si>
-  <si>
-    <t>R$ 8.851,06
-R$ 9.093,08</t>
+    <t>DE LOURDES RAMOS,MARIA</t>
+  </si>
+  <si>
+    <t>215
+173</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>R$ 1.642.339,80</t>
+  </si>
+  <si>
+    <t>R$ 8.877,51
+R$ 9.115,77</t>
   </si>
   <si>
     <t>(4.7%)
 (2.1%)</t>
   </si>
   <si>
-    <t>94.1</t>
-  </si>
-  <si>
-    <t>(6.9%)</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>(40.9%)</t>
+    <t>94.9</t>
+  </si>
+  <si>
+    <t>(6.3%)</t>
+  </si>
+  <si>
+    <t>13.4%</t>
+  </si>
+  <si>
+    <t>(37.4%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -947,31 +950,31 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>32.3</t>
-  </si>
-  <si>
-    <t>57.4%</t>
-  </si>
-  <si>
-    <t>17.7%</t>
-  </si>
-  <si>
-    <t>6.3</t>
+    <t>32.6</t>
+  </si>
+  <si>
+    <t>57.8%</t>
+  </si>
+  <si>
+    <t>18.6%</t>
+  </si>
+  <si>
+    <t>6.5</t>
   </si>
   <si>
     <t>10.4</t>
   </si>
   <si>
-    <t>17.3</t>
-  </si>
-  <si>
-    <t>23.0</t>
-  </si>
-  <si>
-    <t>62.1%</t>
-  </si>
-  <si>
-    <t>-R$ 38.516,61</t>
+    <t>17.5</t>
+  </si>
+  <si>
+    <t>23.3</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>-R$ 38.601,01</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2213,10 +2216,10 @@
         <v>-0.3214285714285714</v>
       </c>
       <c r="T7" s="6">
-        <v>0.61134919360492868</v>
+        <v>0.52664480394795476</v>
       </c>
       <c r="U7" s="6">
-        <v>0.11428822149798826</v>
+        <v>0.029583831841014312</v>
       </c>
       <c r="V7" s="6">
         <v>0.024992988852275119</v>
@@ -5658,7 +5661,7 @@
         <v>19560</v>
       </c>
       <c r="B34" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C34" s="4">
         <v>44</v>
@@ -5694,25 +5697,61 @@
       <c t="s" r="N34" s="4">
         <v>52</v>
       </c>
-      <c r="O34" s="5"/>
-      <c r="P34" s="5"/>
-      <c r="Q34" s="6"/>
-      <c r="R34" s="7"/>
-      <c r="S34" s="6"/>
-      <c r="T34" s="6"/>
-      <c r="U34" s="6"/>
-      <c r="V34" s="6"/>
-      <c r="W34" s="6"/>
-      <c r="X34" s="8"/>
-      <c r="Y34" s="6"/>
-      <c r="Z34" s="6"/>
-      <c r="AA34" s="8"/>
-      <c r="AB34" s="8"/>
-      <c r="AC34" s="8"/>
-      <c r="AD34" s="8"/>
-      <c r="AE34" s="6"/>
+      <c r="O34" s="5">
+        <v>16255.59</v>
+      </c>
+      <c r="P34" s="5">
+        <v>16255.59</v>
+      </c>
+      <c r="Q34" s="6">
+        <v>-0.082003920330658508</v>
+      </c>
+      <c r="R34" s="7">
+        <v>212</v>
+      </c>
+      <c r="S34" s="6">
+        <v>0.1910112359550562</v>
+      </c>
+      <c r="T34" s="6">
+        <v>3.0161007136621922</v>
+      </c>
+      <c r="U34" s="6">
+        <v>2.6728471005973944</v>
+      </c>
+      <c r="V34" s="6">
+        <v>0.053146394563347132</v>
+      </c>
+      <c r="W34" s="6">
+        <v>0.031247466256223246</v>
+      </c>
+      <c r="X34" s="8">
+        <v>38.536199363057321</v>
+      </c>
+      <c r="Y34" s="6">
+        <v>0.7579617834394905</v>
+      </c>
+      <c r="Z34" s="6">
+        <v>0.5286624203821656</v>
+      </c>
+      <c r="AA34" s="8">
+        <v>24.845631067961165</v>
+      </c>
+      <c r="AB34" s="8">
+        <v>2.1344370860927153</v>
+      </c>
+      <c r="AC34" s="8">
+        <v>28.197811999999999</v>
+      </c>
+      <c r="AD34" s="8">
+        <v>33.999893630573247</v>
+      </c>
+      <c r="AE34" s="6">
+        <v>0.37579617834394907</v>
+      </c>
       <c r="AF34" s="9"/>
-      <c r="AG34" s="5"/>
+      <c r="AG34" s="5">
+        <v>-118.40000000000001</v>
+      </c>
       <c r="AH34" s="10">
         <v>4</v>
       </c>
@@ -5888,7 +5927,7 @@
         <v>19562</v>
       </c>
       <c r="B36" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C36" s="4">
         <v>44</v>
@@ -5924,25 +5963,61 @@
       <c t="s" r="N36" s="4">
         <v>52</v>
       </c>
-      <c r="O36" s="5"/>
-      <c r="P36" s="5"/>
-      <c r="Q36" s="6"/>
-      <c r="R36" s="7"/>
-      <c r="S36" s="6"/>
-      <c r="T36" s="6"/>
-      <c r="U36" s="6"/>
-      <c r="V36" s="6"/>
-      <c r="W36" s="6"/>
-      <c r="X36" s="8"/>
-      <c r="Y36" s="6"/>
-      <c r="Z36" s="6"/>
-      <c r="AA36" s="8"/>
-      <c r="AB36" s="8"/>
-      <c r="AC36" s="8"/>
-      <c r="AD36" s="8"/>
-      <c r="AE36" s="6"/>
+      <c r="O36" s="5">
+        <v>7887.1099999999997</v>
+      </c>
+      <c r="P36" s="5">
+        <v>7887.1099999999997</v>
+      </c>
+      <c r="Q36" s="6">
+        <v>0.068077298087861005</v>
+      </c>
+      <c r="R36" s="7">
+        <v>108</v>
+      </c>
+      <c r="S36" s="6">
+        <v>0.63636363636363646</v>
+      </c>
+      <c r="T36" s="6">
+        <v>0.33836784322774754</v>
+      </c>
+      <c r="U36" s="6">
+        <v>0.008004757129037126</v>
+      </c>
+      <c r="V36" s="6">
+        <v>0.054552871710930873</v>
+      </c>
+      <c r="W36" s="6">
+        <v>0.021441884289682786</v>
+      </c>
+      <c r="X36" s="8">
+        <v>51.062186021505376</v>
+      </c>
+      <c r="Y36" s="6">
+        <v>0.63440860215053763</v>
+      </c>
+      <c r="Z36" s="6">
+        <v>0.58064516129032262</v>
+      </c>
+      <c r="AA36" s="8">
+        <v>3.941060909090909</v>
+      </c>
+      <c r="AB36" s="8">
+        <v>31.056883695652171</v>
+      </c>
+      <c r="AC36" s="8">
+        <v>34.803657999999999</v>
+      </c>
+      <c r="AD36" s="8">
+        <v>41.359497849462365</v>
+      </c>
+      <c r="AE36" s="6">
+        <v>0.22580645161290322</v>
+      </c>
       <c r="AF36" s="9"/>
-      <c r="AG36" s="5"/>
+      <c r="AG36" s="5">
+        <v>0</v>
+      </c>
       <c r="AH36" s="10">
         <v>4</v>
       </c>
@@ -10912,7 +10987,7 @@
         <v>19661</v>
       </c>
       <c r="B76" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C76" s="4">
         <v>44</v>
@@ -10946,25 +11021,61 @@
       <c t="s" r="N76" s="4">
         <v>52</v>
       </c>
-      <c r="O76" s="5"/>
-      <c r="P76" s="5"/>
-      <c r="Q76" s="6"/>
-      <c r="R76" s="7"/>
-      <c r="S76" s="6"/>
-      <c r="T76" s="6"/>
-      <c r="U76" s="6"/>
-      <c r="V76" s="6"/>
-      <c r="W76" s="6"/>
-      <c r="X76" s="8"/>
-      <c r="Y76" s="6"/>
-      <c r="Z76" s="6"/>
-      <c r="AA76" s="8"/>
-      <c r="AB76" s="8"/>
-      <c r="AC76" s="8"/>
-      <c r="AD76" s="8"/>
-      <c r="AE76" s="6"/>
+      <c r="O76" s="5">
+        <v>10100.370000000001</v>
+      </c>
+      <c r="P76" s="5">
+        <v>10100.370000000001</v>
+      </c>
+      <c r="Q76" s="6">
+        <v>-0.12207110615857597</v>
+      </c>
+      <c r="R76" s="7">
+        <v>127</v>
+      </c>
+      <c r="S76" s="6">
+        <v>-0.059259259259259234</v>
+      </c>
+      <c r="T76" s="6">
+        <v>0.16692393446972734</v>
+      </c>
+      <c r="U76" s="6">
+        <v>-0.21810552484710954</v>
+      </c>
+      <c r="V76" s="6">
+        <v>0.029464267150609333</v>
+      </c>
+      <c r="W76" s="6">
+        <v>0.0059473068808370382</v>
+      </c>
+      <c r="X76" s="8">
+        <v>43.387088732394368</v>
+      </c>
+      <c r="Y76" s="6">
+        <v>0.29577464788732394</v>
+      </c>
+      <c r="Z76" s="6">
+        <v>0.49295774647887325</v>
+      </c>
+      <c r="AA76" s="8">
+        <v>4.8177000000000003</v>
+      </c>
+      <c r="AB76" s="8">
+        <v>16.145952857142856</v>
+      </c>
+      <c r="AC76" s="8">
+        <v>20.609145999999999</v>
+      </c>
+      <c r="AD76" s="8">
+        <v>29.245539436619719</v>
+      </c>
+      <c r="AE76" s="6">
+        <v>0.23943661971830985</v>
+      </c>
       <c r="AF76" s="9"/>
-      <c r="AG76" s="5"/>
+      <c r="AG76" s="5">
+        <v>34</v>
+      </c>
       <c r="AH76" s="10">
         <v>2</v>
       </c>
@@ -15912,7 +16023,9 @@
       <c r="Z116" s="6"/>
       <c r="AA116" s="8"/>
       <c r="AB116" s="8"/>
-      <c r="AC116" s="8"/>
+      <c r="AC116" s="8">
+        <v>17.310431000000001</v>
+      </c>
       <c r="AD116" s="8"/>
       <c r="AE116" s="6"/>
       <c r="AF116" s="9"/>
@@ -19049,7 +19162,7 @@
         <v>19793</v>
       </c>
       <c r="B141" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C141" s="4">
         <v>44</v>
@@ -19085,25 +19198,61 @@
       <c t="s" r="N141" s="4">
         <v>52</v>
       </c>
-      <c r="O141" s="5"/>
-      <c r="P141" s="5"/>
-      <c r="Q141" s="6"/>
-      <c r="R141" s="7"/>
-      <c r="S141" s="6"/>
-      <c r="T141" s="6"/>
-      <c r="U141" s="6"/>
-      <c r="V141" s="6"/>
-      <c r="W141" s="6"/>
-      <c r="X141" s="8"/>
-      <c r="Y141" s="6"/>
-      <c r="Z141" s="6"/>
-      <c r="AA141" s="8"/>
-      <c r="AB141" s="8"/>
-      <c r="AC141" s="8"/>
-      <c r="AD141" s="8"/>
-      <c r="AE141" s="6"/>
+      <c r="O141" s="5">
+        <v>6054.9099999999999</v>
+      </c>
+      <c r="P141" s="5">
+        <v>6054.9099999999999</v>
+      </c>
+      <c r="Q141" s="6">
+        <v>0.3509091720398918</v>
+      </c>
+      <c r="R141" s="7">
+        <v>76</v>
+      </c>
+      <c r="S141" s="6">
+        <v>0.35714285714285721</v>
+      </c>
+      <c r="T141" s="6">
+        <v>0.33531722189099422</v>
+      </c>
+      <c r="U141" s="6">
+        <v>0.015703883294714539</v>
+      </c>
+      <c r="V141" s="6">
+        <v>0.077262007197464538</v>
+      </c>
+      <c r="W141" s="6">
+        <v>0.038098749609820792</v>
+      </c>
+      <c r="X141" s="8">
+        <v>25.240643859649122</v>
+      </c>
+      <c r="Y141" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z141" s="6">
+        <v>0.017543859649122806</v>
+      </c>
+      <c r="AA141" s="8">
+        <v>5.0230263157894735</v>
+      </c>
+      <c r="AB141" s="8">
+        <v>4.1046789473684209</v>
+      </c>
+      <c r="AC141" s="8">
+        <v>9.3650219999999997</v>
+      </c>
+      <c r="AD141" s="8">
+        <v>17.383333333333333</v>
+      </c>
+      <c r="AE141" s="6">
+        <v>0.78947368421052633</v>
+      </c>
       <c r="AF141" s="9"/>
-      <c r="AG141" s="5"/>
+      <c r="AG141" s="5">
+        <v>0</v>
+      </c>
       <c r="AH141" s="10">
         <v>4</v>
       </c>
@@ -28265,112 +28414,203 @@
         <v>56</v>
       </c>
     </row>
-    <row r="216" ht="24.75" customHeight="1">
-      <c t="s" r="A216" s="14">
+    <row r="216" ht="13.5" customHeight="1">
+      <c r="A216" s="2">
+        <v>19980</v>
+      </c>
+      <c r="B216" s="3">
+        <v>-1</v>
+      </c>
+      <c t="s" r="C216" s="4">
+        <v>44</v>
+      </c>
+      <c t="s" r="D216" s="4">
+        <v>45</v>
+      </c>
+      <c t="s" r="E216" s="4">
+        <v>46</v>
+      </c>
+      <c t="s" r="F216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="G216" s="4">
+        <v>48</v>
+      </c>
+      <c t="s" r="H216" s="4">
+        <v>49</v>
+      </c>
+      <c t="s" r="I216" s="4">
+        <v>50</v>
+      </c>
+      <c t="s" r="J216" s="4">
+        <v>47</v>
+      </c>
+      <c t="s" r="K216" s="4">
+        <v>51</v>
+      </c>
+      <c t="s" r="L216" s="4">
+        <v>51</v>
+      </c>
+      <c r="M216" s="4"/>
+      <c t="s" r="N216" s="4">
+        <v>52</v>
+      </c>
+      <c r="O216" s="5"/>
+      <c r="P216" s="5"/>
+      <c r="Q216" s="6"/>
+      <c r="R216" s="7"/>
+      <c r="S216" s="6"/>
+      <c r="T216" s="6"/>
+      <c r="U216" s="6"/>
+      <c r="V216" s="6"/>
+      <c r="W216" s="6"/>
+      <c r="X216" s="8"/>
+      <c r="Y216" s="6"/>
+      <c r="Z216" s="6"/>
+      <c r="AA216" s="8"/>
+      <c r="AB216" s="8"/>
+      <c r="AC216" s="8"/>
+      <c r="AD216" s="8"/>
+      <c r="AE216" s="6"/>
+      <c r="AF216" s="9"/>
+      <c r="AG216" s="5"/>
+      <c r="AH216" s="10"/>
+      <c r="AI216" s="11"/>
+      <c r="AJ216" s="12"/>
+      <c t="s" r="AK216" s="4">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL216" s="4">
+        <v>52</v>
+      </c>
+      <c r="AM216" s="2">
+        <v>1</v>
+      </c>
+      <c r="AN216" s="2">
+        <v>1</v>
+      </c>
+      <c t="s" r="AO216" s="4">
+        <v>53</v>
+      </c>
+      <c t="s" r="AP216" s="4">
+        <v>54</v>
+      </c>
+      <c t="s" r="AQ216" s="4">
+        <v>55</v>
+      </c>
+      <c t="s" r="AR216" s="4">
         <v>300</v>
       </c>
-      <c t="s" r="B216" s="14">
+      <c t="s" r="AS216" s="4">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="217" ht="24.75" customHeight="1">
+      <c t="s" r="A217" s="14">
         <v>301</v>
       </c>
-      <c r="C216" s="15"/>
-      <c r="D216" s="15"/>
-      <c r="E216" s="15"/>
-      <c r="F216" s="15"/>
-      <c r="G216" s="15"/>
-      <c r="H216" s="15"/>
-      <c r="I216" s="15"/>
-      <c r="J216" s="15"/>
-      <c r="K216" s="15"/>
-      <c r="L216" s="15"/>
-      <c r="M216" s="15"/>
-      <c t="s" r="N216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="O216" s="14">
+      <c t="s" r="B217" s="14">
         <v>302</v>
       </c>
-      <c t="s" r="P216" s="14">
+      <c r="C217" s="15"/>
+      <c r="D217" s="15"/>
+      <c r="E217" s="15"/>
+      <c r="F217" s="15"/>
+      <c r="G217" s="15"/>
+      <c r="H217" s="15"/>
+      <c r="I217" s="15"/>
+      <c r="J217" s="15"/>
+      <c r="K217" s="15"/>
+      <c r="L217" s="15"/>
+      <c r="M217" s="15"/>
+      <c t="s" r="N217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="O217" s="14">
         <v>303</v>
       </c>
-      <c t="s" r="Q216" s="14">
+      <c t="s" r="P217" s="14">
         <v>304</v>
       </c>
-      <c t="s" r="R216" s="14">
+      <c t="s" r="Q217" s="14">
         <v>305</v>
       </c>
-      <c t="s" r="S216" s="14">
+      <c t="s" r="R217" s="14">
         <v>306</v>
       </c>
-      <c t="s" r="T216" s="14">
+      <c t="s" r="S217" s="14">
         <v>307</v>
       </c>
-      <c t="s" r="U216" s="14">
+      <c t="s" r="T217" s="14">
         <v>308</v>
       </c>
-      <c t="s" r="V216" s="14">
+      <c t="s" r="U217" s="14">
         <v>309</v>
       </c>
-      <c t="s" r="W216" s="14">
+      <c t="s" r="V217" s="14">
         <v>310</v>
       </c>
-      <c t="s" r="X216" s="14">
+      <c t="s" r="W217" s="14">
         <v>311</v>
       </c>
-      <c t="s" r="Y216" s="14">
+      <c t="s" r="X217" s="14">
         <v>312</v>
       </c>
-      <c t="s" r="Z216" s="14">
+      <c t="s" r="Y217" s="14">
         <v>313</v>
       </c>
-      <c t="s" r="AA216" s="14">
+      <c t="s" r="Z217" s="14">
         <v>314</v>
       </c>
-      <c t="s" r="AB216" s="14">
+      <c t="s" r="AA217" s="14">
         <v>315</v>
       </c>
-      <c t="s" r="AC216" s="14">
+      <c t="s" r="AB217" s="14">
         <v>316</v>
       </c>
-      <c t="s" r="AD216" s="14">
+      <c t="s" r="AC217" s="14">
         <v>317</v>
       </c>
-      <c t="s" r="AE216" s="14">
+      <c t="s" r="AD217" s="14">
         <v>318</v>
       </c>
-      <c r="AF216" s="14"/>
-      <c t="s" r="AG216" s="14">
+      <c t="s" r="AE217" s="14">
         <v>319</v>
       </c>
-      <c t="s" r="AH216" s="14">
+      <c r="AF217" s="14"/>
+      <c t="s" r="AG217" s="14">
         <v>320</v>
       </c>
-      <c t="s" r="AI216" s="14">
+      <c t="s" r="AH217" s="14">
         <v>321</v>
       </c>
-      <c r="AJ216" s="15"/>
-      <c t="s" r="AK216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AL216" s="15">
-        <v>52</v>
-      </c>
-      <c t="s" r="AM216" s="14">
+      <c t="s" r="AI217" s="14">
         <v>322</v>
       </c>
-      <c t="s" r="AN216" s="14">
-        <v>322</v>
-      </c>
-      <c r="AO216" s="15"/>
-      <c r="AP216" s="15"/>
-      <c r="AQ216" s="15"/>
-      <c r="AR216" s="15"/>
-      <c r="AS216" s="15"/>
+      <c r="AJ217" s="15"/>
+      <c t="s" r="AK217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AL217" s="15">
+        <v>52</v>
+      </c>
+      <c t="s" r="AM217" s="14">
+        <v>323</v>
+      </c>
+      <c t="s" r="AN217" s="14">
+        <v>323</v>
+      </c>
+      <c r="AO217" s="15"/>
+      <c r="AP217" s="15"/>
+      <c r="AQ217" s="15"/>
+      <c r="AR217" s="15"/>
+      <c r="AS217" s="15"/>
     </row>
   </sheetData>
   <pageMargins left="1" right="1" top="1" bottom="1" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
   <ignoredErrors>
-    <ignoredError sqref="A1:AS216" numberStoredAsText="1"/>
+    <ignoredError sqref="A1:AS217" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -915,51 +915,51 @@
   </si>
   <si>
     <t>215
-173</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>R$ 1.642.339,80</t>
-  </si>
-  <si>
-    <t>R$ 8.877,51
-R$ 9.115,77</t>
-  </si>
-  <si>
-    <t>(4.7%)
-(2.1%)</t>
-  </si>
-  <si>
-    <t>94.9</t>
-  </si>
-  <si>
-    <t>(6.3%)</t>
-  </si>
-  <si>
-    <t>13.4%</t>
-  </si>
-  <si>
-    <t>(37.4%)</t>
+174</t>
+  </si>
+  <si>
+    <t>29</t>
+  </si>
+  <si>
+    <t>R$ 1.659.784,52</t>
+  </si>
+  <si>
+    <t>R$ 8.923,57
+R$ 9.163,64</t>
+  </si>
+  <si>
+    <t>(4.6%)
+(2.0%)</t>
+  </si>
+  <si>
+    <t>95.3</t>
+  </si>
+  <si>
+    <t>(6.2%)</t>
+  </si>
+  <si>
+    <t>13.6%</t>
+  </si>
+  <si>
+    <t>(37.0%)</t>
   </si>
   <si>
     <t>2.7%</t>
   </si>
   <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>32.6</t>
-  </si>
-  <si>
-    <t>57.8%</t>
-  </si>
-  <si>
-    <t>18.6%</t>
-  </si>
-  <si>
-    <t>6.5</t>
+    <t>0.6%</t>
+  </si>
+  <si>
+    <t>32.9</t>
+  </si>
+  <si>
+    <t>57.2%</t>
+  </si>
+  <si>
+    <t>19.3%</t>
+  </si>
+  <si>
+    <t>6.6</t>
   </si>
   <si>
     <t>10.4</t>
@@ -968,13 +968,13 @@
     <t>17.5</t>
   </si>
   <si>
-    <t>23.3</t>
-  </si>
-  <si>
-    <t>61.3%</t>
-  </si>
-  <si>
-    <t>-R$ 38.601,01</t>
+    <t>23.5</t>
+  </si>
+  <si>
+    <t>60.6%</t>
+  </si>
+  <si>
+    <t>-R$ 38.630,91</t>
   </si>
   <si>
     <t>2.94</t>
@@ -11077,7 +11077,7 @@
         <v>34</v>
       </c>
       <c r="AH76" s="10">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI76" s="11"/>
       <c r="AJ76" s="13">
@@ -16553,7 +16553,7 @@
         <v>-80.25</v>
       </c>
       <c r="AH120" s="10">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI120" s="11"/>
       <c r="AJ120" s="13">
@@ -21412,7 +21412,7 @@
         <v>19863</v>
       </c>
       <c r="B159" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C159" s="4">
         <v>44</v>
@@ -21448,27 +21448,61 @@
       <c t="s" r="N159" s="4">
         <v>52</v>
       </c>
-      <c r="O159" s="5"/>
-      <c r="P159" s="5"/>
-      <c r="Q159" s="6"/>
-      <c r="R159" s="7"/>
-      <c r="S159" s="6"/>
-      <c r="T159" s="6"/>
-      <c r="U159" s="6"/>
-      <c r="V159" s="6"/>
-      <c r="W159" s="6"/>
-      <c r="X159" s="8"/>
-      <c r="Y159" s="6"/>
-      <c r="Z159" s="6"/>
-      <c r="AA159" s="8"/>
-      <c r="AB159" s="8"/>
+      <c r="O159" s="5">
+        <v>17444.720000000001</v>
+      </c>
+      <c r="P159" s="5">
+        <v>17444.720000000001</v>
+      </c>
+      <c r="Q159" s="6">
+        <v>0.072845833054022036</v>
+      </c>
+      <c r="R159" s="7">
+        <v>173</v>
+      </c>
+      <c r="S159" s="6">
+        <v>0.10897435897435903</v>
+      </c>
+      <c r="T159" s="6">
+        <v>0.27854362236825808</v>
+      </c>
+      <c r="U159" s="6">
+        <v>-0.010814991584846303</v>
+      </c>
+      <c r="V159" s="6">
+        <v>0.03025499979363383</v>
+      </c>
+      <c r="W159" s="6">
+        <v>0.012087324990025634</v>
+      </c>
+      <c r="X159" s="8">
+        <v>59.004662237762233</v>
+      </c>
+      <c r="Y159" s="6">
+        <v>0.11888111888111888</v>
+      </c>
+      <c r="Z159" s="6">
+        <v>0.78321678321678323</v>
+      </c>
+      <c r="AA159" s="8">
+        <v>16.396666470588237</v>
+      </c>
+      <c r="AB159" s="8">
+        <v>11.122262142857144</v>
+      </c>
       <c r="AC159" s="8">
         <v>29.230885000000001</v>
       </c>
-      <c r="AD159" s="8"/>
-      <c r="AE159" s="6"/>
+      <c r="AD159" s="8">
+        <v>36.05492957746479</v>
+      </c>
+      <c r="AE159" s="6">
+        <v>0.1048951048951049</v>
+      </c>
       <c r="AF159" s="9"/>
-      <c r="AG159" s="5"/>
+      <c r="AG159" s="5">
+        <v>-29.899999999999999</v>
+      </c>
       <c r="AH159" s="10">
         <v>2</v>
       </c>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -915,30 +915,30 @@
   </si>
   <si>
     <t>215
-174</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>R$ 1.659.784,52</t>
-  </si>
-  <si>
-    <t>R$ 8.923,57
-R$ 9.163,64</t>
-  </si>
-  <si>
-    <t>(4.6%)
-(2.0%)</t>
-  </si>
-  <si>
-    <t>95.3</t>
-  </si>
-  <si>
-    <t>(6.2%)</t>
-  </si>
-  <si>
-    <t>13.6%</t>
+175</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>R$ 1.665.384,37</t>
+  </si>
+  <si>
+    <t>R$ 8.905,80
+R$ 9.143,28</t>
+  </si>
+  <si>
+    <t>(5.0%)
+(2.5%)</t>
+  </si>
+  <si>
+    <t>95.1</t>
+  </si>
+  <si>
+    <t>(6.5%)</t>
+  </si>
+  <si>
+    <t>13.5%</t>
   </si>
   <si>
     <t>(37.0%)</t>
@@ -947,13 +947,13 @@
     <t>2.7%</t>
   </si>
   <si>
-    <t>0.6%</t>
+    <t>0.5%</t>
   </si>
   <si>
     <t>32.9</t>
   </si>
   <si>
-    <t>57.2%</t>
+    <t>57.3%</t>
   </si>
   <si>
     <t>19.3%</t>
@@ -968,10 +968,10 @@
     <t>17.5</t>
   </si>
   <si>
-    <t>23.5</t>
-  </si>
-  <si>
-    <t>60.6%</t>
+    <t>23.4</t>
+  </si>
+  <si>
+    <t>60.7%</t>
   </si>
   <si>
     <t>-R$ 38.630,91</t>
@@ -4840,7 +4840,7 @@
         <v>-543.32000000000005</v>
       </c>
       <c r="AH27" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI27" s="11"/>
       <c r="AJ27" s="13">
@@ -12640,7 +12640,7 @@
         <v>19693</v>
       </c>
       <c r="B89" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C89" s="4">
         <v>44</v>
@@ -12674,25 +12674,59 @@
       <c t="s" r="N89" s="4">
         <v>52</v>
       </c>
-      <c r="O89" s="5"/>
-      <c r="P89" s="5"/>
-      <c r="Q89" s="6"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="6"/>
-      <c r="T89" s="6"/>
-      <c r="U89" s="6"/>
-      <c r="V89" s="6"/>
-      <c r="W89" s="6"/>
-      <c r="X89" s="8"/>
-      <c r="Y89" s="6"/>
-      <c r="Z89" s="6"/>
-      <c r="AA89" s="8"/>
-      <c r="AB89" s="8"/>
+      <c r="O89" s="5">
+        <v>5599.8500000000004</v>
+      </c>
+      <c r="P89" s="5">
+        <v>5599.8500000000004</v>
+      </c>
+      <c r="Q89" s="6">
+        <v>-0.5701397236845539</v>
+      </c>
+      <c r="R89" s="7">
+        <v>55</v>
+      </c>
+      <c r="S89" s="6">
+        <v>-0.52991452991452992</v>
+      </c>
+      <c r="T89" s="6">
+        <v>0.013714831647276266</v>
+      </c>
+      <c r="U89" s="6">
+        <v>-0.31995839174263596</v>
+      </c>
+      <c r="V89" s="6">
+        <v>0.017262694536460794</v>
+      </c>
+      <c r="W89" s="6">
+        <v>-0.0033235711670848325</v>
+      </c>
+      <c r="X89" s="8">
+        <v>25.883333333333333</v>
+      </c>
+      <c r="Y89" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z89" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA89" s="8">
+        <v>3.4818719298245613</v>
+      </c>
+      <c r="AB89" s="8">
+        <v>13.054545454545455</v>
+      </c>
       <c r="AC89" s="8"/>
-      <c r="AD89" s="8"/>
-      <c r="AE89" s="6"/>
+      <c r="AD89" s="8">
+        <v>20.337780000000002</v>
+      </c>
+      <c r="AE89" s="6">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="AF89" s="9"/>
-      <c r="AG89" s="5"/>
+      <c r="AG89" s="5">
+        <v>0</v>
+      </c>
       <c r="AH89" s="10">
         <v>2</v>
       </c>
@@ -14222,7 +14256,7 @@
         <v>-22.800000000000001</v>
       </c>
       <c r="AH101" s="10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AI101" s="11"/>
       <c r="AJ101" s="13">
@@ -24762,7 +24796,7 @@
         <v>19923</v>
       </c>
       <c r="B185" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C185" s="4">
         <v>44</v>
@@ -25733,7 +25767,7 @@
         <v>0</v>
       </c>
       <c r="AH192" s="10">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI192" s="11"/>
       <c r="AJ192" s="13">
@@ -27044,7 +27078,7 @@
         <v>19957</v>
       </c>
       <c r="B203" s="3">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c t="s" r="C203" s="4">
         <v>44</v>
@@ -28453,7 +28487,7 @@
         <v>19980</v>
       </c>
       <c r="B216" s="3">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c t="s" r="C216" s="4">
         <v>44</v>

--- a/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
+++ b/dados_all_stores/Keys Summary - All Stores (Stores) (2026-10-09).xlsx
@@ -915,33 +915,33 @@
   </si>
   <si>
     <t>215
-175</t>
-  </si>
-  <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>R$ 1.665.384,37</t>
-  </si>
-  <si>
-    <t>R$ 8.905,80
-R$ 9.143,28</t>
-  </si>
-  <si>
-    <t>(5.0%)
-(2.5%)</t>
-  </si>
-  <si>
-    <t>95.1</t>
-  </si>
-  <si>
-    <t>(6.5%)</t>
-  </si>
-  <si>
-    <t>13.5%</t>
-  </si>
-  <si>
-    <t>(37.0%)</t>
+181</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>R$ 1.713.181,22</t>
+  </si>
+  <si>
+    <t>R$ 8.876,59
+R$ 9.104,25</t>
+  </si>
+  <si>
+    <t>(5.2%)
+(2.7%)</t>
+  </si>
+  <si>
+    <t>94.6</t>
+  </si>
+  <si>
+    <t>(6.6%)</t>
+  </si>
+  <si>
+    <t>13.9%</t>
+  </si>
+  <si>
+    <t>(36.0%)</t>
   </si>
   <si>
     <t>2.7%</t>
@@ -950,31 +950,31 @@
     <t>0.5%</t>
   </si>
   <si>
-    <t>32.9</t>
-  </si>
-  <si>
-    <t>57.3%</t>
-  </si>
-  <si>
-    <t>19.3%</t>
-  </si>
-  <si>
-    <t>6.6</t>
-  </si>
-  <si>
-    <t>10.4</t>
-  </si>
-  <si>
-    <t>17.5</t>
-  </si>
-  <si>
-    <t>23.4</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>-R$ 38.630,91</t>
+    <t>33.2</t>
+  </si>
+  <si>
+    <t>56.9%</t>
+  </si>
+  <si>
+    <t>19.4%</t>
+  </si>
+  <si>
+    <t>6.7</t>
+  </si>
+  <si>
+    <t>10.5</t>
+  </si>
+  <si>
+    <t>17.7</t>
+  </si>
+  <si>
+    <t>23.7</t>
+  </si>
+  <si>
+    <t>60.4%</t>
+  </si>
+  <si>
+    <t>-R$ 39.013,21</t>
   </si>
   <si>
     <t>2.94</t>
@@ -2069,7 +2069,7 @@
         <v>19507</v>
       </c>
       <c r="B6" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C6" s="4">
         <v>44</v>
@@ -2105,25 +2105,61 @@
       <c t="s" r="N6" s="4">
         <v>52</v>
       </c>
-      <c r="O6" s="5"/>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="6"/>
-      <c r="R6" s="7"/>
-      <c r="S6" s="6"/>
-      <c r="T6" s="6"/>
-      <c r="U6" s="6"/>
-      <c r="V6" s="6"/>
-      <c r="W6" s="6"/>
-      <c r="X6" s="8"/>
-      <c r="Y6" s="6"/>
-      <c r="Z6" s="6"/>
-      <c r="AA6" s="8"/>
-      <c r="AB6" s="8"/>
-      <c r="AC6" s="8"/>
-      <c r="AD6" s="8"/>
-      <c r="AE6" s="6"/>
+      <c r="O6" s="5">
+        <v>13204.709999999999</v>
+      </c>
+      <c r="P6" s="5">
+        <v>13204.709999999999</v>
+      </c>
+      <c r="Q6" s="6">
+        <v>-0.19938799279948738</v>
+      </c>
+      <c r="R6" s="7">
+        <v>126</v>
+      </c>
+      <c r="S6" s="6">
+        <v>-0.19230769230769229</v>
+      </c>
+      <c r="T6" s="6">
+        <v>0.27452455222416849</v>
+      </c>
+      <c r="U6" s="6">
+        <v>0.012155291558845292</v>
+      </c>
+      <c r="V6" s="6">
+        <v>0.031146628740805364</v>
+      </c>
+      <c r="W6" s="6">
+        <v>0.0062729283717703763</v>
+      </c>
+      <c r="X6" s="8">
+        <v>22.630876842105266</v>
+      </c>
+      <c r="Y6" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8">
+        <v>6.9124999999999996</v>
+      </c>
+      <c r="AB6" s="8">
+        <v>1.896098936170213</v>
+      </c>
+      <c r="AC6" s="8">
+        <v>8.7659230000000008</v>
+      </c>
+      <c r="AD6" s="8">
+        <v>15.688947368421053</v>
+      </c>
+      <c r="AE6" s="6">
+        <v>0.94736842105263153</v>
+      </c>
       <c r="AF6" s="9"/>
-      <c r="AG6" s="5"/>
+      <c r="AG6" s="5">
+        <v>-169.59999999999999</v>
+      </c>
       <c r="AH6" s="10">
         <v>5</v>
       </c>
@@ -7886,7 +7922,7 @@
         <v>19602</v>
       </c>
       <c r="B51" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C51" s="4">
         <v>44</v>
@@ -7922,25 +7958,59 @@
       <c t="s" r="N51" s="4">
         <v>52</v>
       </c>
-      <c r="O51" s="5"/>
-      <c r="P51" s="5"/>
-      <c r="Q51" s="6"/>
-      <c r="R51" s="7"/>
-      <c r="S51" s="6"/>
-      <c r="T51" s="6"/>
-      <c r="U51" s="6"/>
-      <c r="V51" s="6"/>
-      <c r="W51" s="6"/>
-      <c r="X51" s="8"/>
-      <c r="Y51" s="6"/>
-      <c r="Z51" s="6"/>
-      <c r="AA51" s="8"/>
-      <c r="AB51" s="8"/>
+      <c r="O51" s="5">
+        <v>1220.5999999999999</v>
+      </c>
+      <c r="P51" s="5">
+        <v>1220.5999999999999</v>
+      </c>
+      <c r="Q51" s="6">
+        <v>-0.042486428817973598</v>
+      </c>
+      <c r="R51" s="7">
+        <v>12</v>
+      </c>
+      <c r="S51" s="6">
+        <v>-0.1428571428571429</v>
+      </c>
+      <c r="T51" s="6">
+        <v>0</v>
+      </c>
+      <c r="U51" s="6">
+        <v>-0.36047845321972805</v>
+      </c>
+      <c r="V51" s="6">
+        <v>0.025905292479108638</v>
+      </c>
+      <c r="W51" s="6">
+        <v>-0.089742749467475028</v>
+      </c>
+      <c r="X51" s="8">
+        <v>37.246660000000006</v>
+      </c>
+      <c r="Y51" s="6">
+        <v>1</v>
+      </c>
+      <c r="Z51" s="6">
+        <v>0.20000000000000001</v>
+      </c>
+      <c r="AA51" s="8">
+        <v>5.3694416666666669</v>
+      </c>
+      <c r="AB51" s="8">
+        <v>23.06334</v>
+      </c>
       <c r="AC51" s="8"/>
-      <c r="AD51" s="8"/>
-      <c r="AE51" s="6"/>
+      <c r="AD51" s="8">
+        <v>35.646660000000004</v>
+      </c>
+      <c r="AE51" s="6">
+        <v>0.59999999999999998</v>
+      </c>
       <c r="AF51" s="9"/>
-      <c r="AG51" s="5"/>
+      <c r="AG51" s="5">
+        <v>0</v>
+      </c>
       <c r="AH51" s="10">
         <v>2</v>
       </c>
@@ -8813,7 +8883,9 @@
       <c r="Z58" s="6"/>
       <c r="AA58" s="8"/>
       <c r="AB58" s="8"/>
-      <c r="AC58" s="8"/>
+      <c r="AC58" s="8">
+        <v>12.441038000000001</v>
+      </c>
       <c r="AD58" s="8"/>
       <c r="AE58" s="6"/>
       <c r="AF58" s="9"/>
@@ -20506,7 +20578,7 @@
         <v>19821</v>
       </c>
       <c r="B151" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C151" s="4">
         <v>44</v>
@@ -20542,25 +20614,61 @@
       <c t="s" r="N151" s="4">
         <v>52</v>
       </c>
-      <c r="O151" s="5"/>
-      <c r="P151" s="5"/>
-      <c r="Q151" s="6"/>
-      <c r="R151" s="7"/>
-      <c r="S151" s="6"/>
-      <c r="T151" s="6"/>
-      <c r="U151" s="6"/>
-      <c r="V151" s="6"/>
-      <c r="W151" s="6"/>
-      <c r="X151" s="8"/>
-      <c r="Y151" s="6"/>
-      <c r="Z151" s="6"/>
-      <c r="AA151" s="8"/>
-      <c r="AB151" s="8"/>
-      <c r="AC151" s="8"/>
-      <c r="AD151" s="8"/>
-      <c r="AE151" s="6"/>
+      <c r="O151" s="5">
+        <v>6397.3400000000001</v>
+      </c>
+      <c r="P151" s="5">
+        <v>6397.3400000000001</v>
+      </c>
+      <c r="Q151" s="6">
+        <v>-0.34900575250100996</v>
+      </c>
+      <c r="R151" s="7">
+        <v>66</v>
+      </c>
+      <c r="S151" s="6">
+        <v>-0.3529411764705882</v>
+      </c>
+      <c r="T151" s="6">
+        <v>0.23236021533950046</v>
+      </c>
+      <c r="U151" s="6">
+        <v>-0.067242432010804487</v>
+      </c>
+      <c r="V151" s="6">
+        <v>0.048593399756773903</v>
+      </c>
+      <c r="W151" s="6">
+        <v>0.02331101676634351</v>
+      </c>
+      <c r="X151" s="8">
+        <v>26.398563793103449</v>
+      </c>
+      <c r="Y151" s="6">
+        <v>0.55172413793103448</v>
+      </c>
+      <c r="Z151" s="6">
+        <v>0.017241379310344827</v>
+      </c>
+      <c r="AA151" s="8">
+        <v>7.0121212121212126</v>
+      </c>
+      <c r="AB151" s="8">
+        <v>2.503869642857143</v>
+      </c>
+      <c r="AC151" s="8">
+        <v>9.9676620000000007</v>
+      </c>
+      <c r="AD151" s="8">
+        <v>16.715805172413795</v>
+      </c>
+      <c r="AE151" s="6">
+        <v>0.68965517241379315</v>
+      </c>
       <c r="AF151" s="9"/>
-      <c r="AG151" s="5"/>
+      <c r="AG151" s="5">
+        <v>-116.90000000000001</v>
+      </c>
       <c r="AH151" s="10">
         <v>5</v>
       </c>
@@ -21256,7 +21364,7 @@
         <v>19855</v>
       </c>
       <c r="B157" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C157" s="4">
         <v>44</v>
@@ -21292,25 +21400,61 @@
       <c t="s" r="N157" s="4">
         <v>52</v>
       </c>
-      <c r="O157" s="5"/>
-      <c r="P157" s="5"/>
-      <c r="Q157" s="6"/>
-      <c r="R157" s="7"/>
-      <c r="S157" s="6"/>
-      <c r="T157" s="6"/>
-      <c r="U157" s="6"/>
-      <c r="V157" s="6"/>
-      <c r="W157" s="6"/>
-      <c r="X157" s="8"/>
-      <c r="Y157" s="6"/>
-      <c r="Z157" s="6"/>
-      <c r="AA157" s="8"/>
-      <c r="AB157" s="8"/>
-      <c r="AC157" s="8"/>
-      <c r="AD157" s="8"/>
-      <c r="AE157" s="6"/>
+      <c r="O157" s="5">
+        <v>7236.8400000000001</v>
+      </c>
+      <c r="P157" s="5">
+        <v>7236.8400000000001</v>
+      </c>
+      <c r="Q157" s="6">
+        <v>-0.04286377469438285</v>
+      </c>
+      <c r="R157" s="7">
+        <v>75</v>
+      </c>
+      <c r="S157" s="6">
+        <v>0</v>
+      </c>
+      <c r="T157" s="6">
+        <v>0.31646313860745851</v>
+      </c>
+      <c r="U157" s="6">
+        <v>0.0088827582204387551</v>
+      </c>
+      <c r="V157" s="6">
+        <v>0.031953794750194837</v>
+      </c>
+      <c r="W157" s="6">
+        <v>0.013040843793700012</v>
+      </c>
+      <c r="X157" s="8">
+        <v>27.427692307692308</v>
+      </c>
+      <c r="Y157" s="6">
+        <v>0.30769230769230771</v>
+      </c>
+      <c r="Z157" s="6">
+        <v>0.015384615384615385</v>
+      </c>
+      <c r="AA157" s="8">
+        <v>11.225555999999999</v>
+      </c>
+      <c r="AB157" s="8">
+        <v>2.2182162790697677</v>
+      </c>
+      <c r="AC157" s="8">
+        <v>14.150268000000001</v>
+      </c>
+      <c r="AD157" s="8">
+        <v>18.92512769230769</v>
+      </c>
+      <c r="AE157" s="6">
+        <v>0.58461538461538465</v>
+      </c>
       <c r="AF157" s="9"/>
-      <c r="AG157" s="5"/>
+      <c r="AG157" s="5">
+        <v>0</v>
+      </c>
       <c r="AH157" s="10">
         <v>4</v>
       </c>
@@ -21351,7 +21495,7 @@
         <v>19859</v>
       </c>
       <c r="B158" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C158" s="4">
         <v>44</v>
@@ -21387,25 +21531,61 @@
       <c t="s" r="N158" s="4">
         <v>52</v>
       </c>
-      <c r="O158" s="5"/>
-      <c r="P158" s="5"/>
-      <c r="Q158" s="6"/>
-      <c r="R158" s="7"/>
-      <c r="S158" s="6"/>
-      <c r="T158" s="6"/>
-      <c r="U158" s="6"/>
-      <c r="V158" s="6"/>
-      <c r="W158" s="6"/>
-      <c r="X158" s="8"/>
-      <c r="Y158" s="6"/>
-      <c r="Z158" s="6"/>
-      <c r="AA158" s="8"/>
-      <c r="AB158" s="8"/>
-      <c r="AC158" s="8"/>
-      <c r="AD158" s="8"/>
-      <c r="AE158" s="6"/>
+      <c r="O158" s="5">
+        <v>7468.1800000000003</v>
+      </c>
+      <c r="P158" s="5">
+        <v>7468.1800000000003</v>
+      </c>
+      <c r="Q158" s="6">
+        <v>-0.28106309222059311</v>
+      </c>
+      <c r="R158" s="7">
+        <v>71</v>
+      </c>
+      <c r="S158" s="6">
+        <v>-0.32380952380952377</v>
+      </c>
+      <c r="T158" s="6">
+        <v>0.31390937283247056</v>
+      </c>
+      <c r="U158" s="6">
+        <v>0.0082940823600930868</v>
+      </c>
+      <c r="V158" s="6">
+        <v>0.019660881232107418</v>
+      </c>
+      <c r="W158" s="6">
+        <v>-0.0012424713919589512</v>
+      </c>
+      <c r="X158" s="8">
+        <v>38.204401886792454</v>
+      </c>
+      <c r="Y158" s="6">
+        <v>0.13207547169811321</v>
+      </c>
+      <c r="Z158" s="6">
+        <v>0.32075471698113206</v>
+      </c>
+      <c r="AA158" s="8">
+        <v>11.71338028169014</v>
+      </c>
+      <c r="AB158" s="8">
+        <v>8.1512584905660379</v>
+      </c>
+      <c r="AC158" s="8">
+        <v>20.912984999999999</v>
+      </c>
+      <c r="AD158" s="8">
+        <v>26.263835849056605</v>
+      </c>
+      <c r="AE158" s="6">
+        <v>0.22641509433962265</v>
+      </c>
       <c r="AF158" s="9"/>
-      <c r="AG158" s="5"/>
+      <c r="AG158" s="5">
+        <v>0</v>
+      </c>
       <c r="AH158" s="10">
         <v>2</v>
       </c>
@@ -22222,7 +22402,7 @@
         <v>19877</v>
       </c>
       <c r="B165" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="s" r="C165" s="4">
         <v>44</v>
@@ -22258,25 +22438,61 @@
       <c t="s" r="N165" s="4">
         <v>52</v>
       </c>
-      <c r="O165" s="5"/>
-      <c r="P165" s="5"/>
-      <c r="Q165" s="6"/>
-      <c r="R165" s="7"/>
-      <c r="S165" s="6"/>
-      <c r="T165" s="6"/>
-      <c r="U165" s="6"/>
-      <c r="V165" s="6"/>
-      <c r="W165" s="6"/>
-      <c r="X165" s="8"/>
-      <c r="Y165" s="6"/>
-      <c r="Z165" s="6"/>
-      <c r="AA165" s="8"/>
-      <c r="AB165" s="8"/>
-      <c r="AC165" s="8"/>
-      <c r="AD165" s="8"/>
-      <c r="AE165" s="6"/>
+      <c r="O165" s="5">
+        <v>12269.18</v>
+      </c>
+      <c r="P165" s="5">
+        <v>12269.18</v>
+      </c>
+      <c r="Q165" s="6">
+        <v>0.59674279140226028</v>
+      </c>
+      <c r="R165" s="7">
+        <v>130</v>
+      </c>
+      <c r="S165" s="6">
+        <v>0.38297872340425543</v>
+      </c>
+      <c r="T165" s="6">
+        <v>0.30367600768755532</v>
+      </c>
+      <c r="U165" s="6">
+        <v>-0.0049990626920462496</v>
+      </c>
+      <c r="V165" s="6">
+        <v>0.01678205063419071</v>
+      </c>
+      <c r="W165" s="6">
+        <v>-0.001862227141504159</v>
+      </c>
+      <c r="X165" s="8">
+        <v>78.731770833333329</v>
+      </c>
+      <c r="Y165" s="6">
+        <v>0.10416666666666667</v>
+      </c>
+      <c r="Z165" s="6">
+        <v>0.64583333333333337</v>
+      </c>
+      <c r="AA165" s="8">
+        <v>19.321930075187968</v>
+      </c>
+      <c r="AB165" s="8">
+        <v>31.268750000000001</v>
+      </c>
+      <c r="AC165" s="8">
+        <v>55.843834999999999</v>
+      </c>
+      <c r="AD165" s="8">
+        <v>62.551215624999998</v>
+      </c>
+      <c r="AE165" s="6">
+        <v>0.1875</v>
+      </c>
       <c r="AF165" s="9"/>
-      <c r="AG165" s="5"/>
+      <c r="AG165" s="5">
+        <v>-95.799999999999997</v>
+      </c>
       <c r="AH165" s="10">
         <v>3</v>
       </c>
